--- a/tiflow-core/develop/1.0.0-draft/StructureDefinition-GEM-ERP-PR-Task.xlsx
+++ b/tiflow-core/develop/1.0.0-draft/StructureDefinition-GEM-ERP-PR-Task.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5226" uniqueCount="749">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5246" uniqueCount="762">
   <si>
     <t>Property</t>
   </si>
@@ -499,6 +499,16 @@
     <t>Meta.security</t>
   </si>
   <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
+    <t>CV</t>
+  </si>
+  <si>
+    <t>CE/CNE/CWE subset one of the sets of component 1-3 or 4-6</t>
+  </si>
+  <si>
     <t>Task.meta.tag</t>
   </si>
   <si>
@@ -627,9 +637,6 @@
     <t>An Extension</t>
   </si>
   <si>
-    <t>Erweiterungen für die Aufgabe, die durch url unterschieden werden.</t>
-  </si>
-  <si>
     <t>DomainResource.extension</t>
   </si>
   <si>
@@ -649,10 +656,6 @@
     <t>Definiert den Typ des Rezepts. Das Codesystem enthält alle unterstützten Formulare.</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
     <t>Task.extension:acceptDate</t>
   </si>
   <si>
@@ -778,6 +781,9 @@
     <t>FiveWs.identifier</t>
   </si>
   <si>
+    <t>CX / EI (occasionally, more often EI maps to a resource id or a URL)</t>
+  </si>
+  <si>
     <t>Task.identifier:PrescriptionID</t>
   </si>
   <si>
@@ -961,7 +967,15 @@
     <t>Time period during which identifier is/was valid for use.</t>
   </si>
   <si>
+    <t>A Period specifies a range of time; the context of use will specify whether the entire range applies (e.g. "the patient was an inpatient of the hospital for this time range") or one value from the range applies (e.g. "give to the patient between these two times").
+Period is not used for a duration (a measure of elapsed time). See [Duration](http://hl7.org/fhir/R4/datatypes.html#Duration).</t>
+  </si>
+  <si>
     <t>Identifier.period</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+per-1:If present, start SHALL have a lower value than end {start.hasValue().not() or end.hasValue().not() or (start &lt;= end)}</t>
   </si>
   <si>
     <t>Role.effectiveTime or implied by context</t>
@@ -992,6 +1006,10 @@
     <t>Identifier.assigner</t>
   </si>
   <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
+  </si>
+  <si>
     <t>II.assigningAuthorityName but note that this is an improper use by the definition of the field.  Also Role.scoper</t>
   </si>
   <si>
@@ -1021,6 +1039,9 @@
     <t>The URL pointing to a *FHIR*-defined protocol, guideline, orderset or other definition that is adhered to in whole or in part by this Task.</t>
   </si>
   <si>
+    <t>see [Canonical References](http://hl7.org/fhir/R4/references.html#canonical)</t>
+  </si>
+  <si>
     <t>Enables a formal definition of how he task is to be performed, enabling automation.</t>
   </si>
   <si>
@@ -1034,6 +1055,9 @@
   </si>
   <si>
     <t>The URL pointing to an *externally* maintained  protocol, guideline, orderset or other definition that is adhered to in whole or in part by this Task.</t>
+  </si>
+  <si>
+    <t>see http://en.wikipedia.org/wiki/Uniform_resource_identifier</t>
   </si>
   <si>
     <t>Enables a formal definition of how he task is to be performed (e.g. using BPMN, BPEL, XPDL or other formal notation to be associated with a task), enabling automation.</t>
@@ -1055,6 +1079,9 @@
     <t>BasedOn refers to a higher-level authorization that triggered the creation of the task.  It references a "request" resource such as a ServiceRequest, MedicationRequest, ServiceRequest, CarePlan, etc. which is distinct from the "request" resource the task is seeking to fulfill.  This latter resource is referenced by FocusOn.  For example, based on a ServiceRequest (= BasedOn), a task is created to fulfill a procedureRequest ( = FocusOn ) to collect a specimen from a patient.</t>
   </si>
   <si>
+    <t>References SHALL be a reference to an actual FHIR resource, and SHALL be resolveable (allowing for access control, temporary unavailability, etc.). Resolution can be either by retrieval from the URL, or, where applicable by resource type, by treating an absolute reference as a canonical URL and looking it up in a local registry/repository.</t>
+  </si>
+  <si>
     <t>Request.basedOn, Event.basedOn</t>
   </si>
   <si>
@@ -1146,6 +1173,9 @@
     <t>.inboundRelationship[typeCode=SUBJ].source[classCode=CACT, moodCode=EVN, code="status change"].reasonCode</t>
   </si>
   <si>
+    <t>CE/CNE/CWE</t>
+  </si>
+  <si>
     <t>Task.businessStatus</t>
   </si>
   <si>
@@ -1153,6 +1183,9 @@
   </si>
   <si>
     <t>Contains business-specific nuances of the business state.</t>
+  </si>
+  <si>
+    <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.</t>
   </si>
   <si>
     <t>There's often a need to track substates of a task - this is often variable by specific workflow implementation.</t>
@@ -1259,6 +1292,9 @@
   </si>
   <si>
     <t>A free-text description of what is to be performed.</t>
+  </si>
+  <si>
+    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
   </si>
   <si>
     <t>.text</t>
@@ -1437,6 +1473,9 @@
     <t>FiveWs.done[x]</t>
   </si>
   <si>
+    <t>DR</t>
+  </si>
+  <si>
     <t>Task.authoredOn</t>
   </si>
   <si>
@@ -1727,6 +1766,9 @@
   </si>
   <si>
     <t>Free-text information captured about the task as it progresses.</t>
+  </si>
+  <si>
+    <t>For systems that do not have structured annotations, they can simply communicate a single annotation with no author or time.  This element may need to be included in narrative because of the potential for modifying information.  *Annotations SHOULD NOT* be used to communicate "modifying" information that could be computable. (This is a SHOULD because enforcing user behavior is nearly impossible).</t>
   </si>
   <si>
     <t>Request.note, Event.note</t>
@@ -2693,7 +2735,7 @@
     <col min="37" max="37" width="47.7734375" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="94.296875" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="31.65234375" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="39.109375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="53.91015625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4050,7 +4092,7 @@
         <v>79</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>99</v>
@@ -4059,21 +4101,21 @@
         <v>77</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>77</v>
+        <v>156</v>
       </c>
       <c r="AM12" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>77</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -4099,13 +4141,13 @@
         <v>147</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -4131,13 +4173,13 @@
         <v>77</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>77</v>
@@ -4155,7 +4197,7 @@
         <v>77</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>78</v>
@@ -4164,7 +4206,7 @@
         <v>79</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AJ13" t="s" s="2">
         <v>99</v>
@@ -4173,21 +4215,21 @@
         <v>77</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>77</v>
+        <v>156</v>
       </c>
       <c r="AM13" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>77</v>
+        <v>157</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -4213,13 +4255,13 @@
         <v>129</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -4269,7 +4311,7 @@
         <v>77</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
@@ -4298,10 +4340,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -4324,16 +4366,16 @@
         <v>77</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -4359,13 +4401,13 @@
         <v>77</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>77</v>
@@ -4383,7 +4425,7 @@
         <v>77</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
@@ -4412,14 +4454,14 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -4438,16 +4480,16 @@
         <v>77</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -4497,7 +4539,7 @@
         <v>77</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
@@ -4515,7 +4557,7 @@
         <v>77</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>77</v>
@@ -4526,14 +4568,14 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -4552,16 +4594,16 @@
         <v>77</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -4611,7 +4653,7 @@
         <v>77</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
@@ -4629,7 +4671,7 @@
         <v>77</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>77</v>
@@ -4640,10 +4682,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4669,10 +4711,10 @@
         <v>108</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -4714,7 +4756,7 @@
         <v>112</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>196</v>
+        <v>113</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>77</v>
@@ -4723,7 +4765,7 @@
         <v>141</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -4752,13 +4794,13 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D19" t="s" s="2">
         <v>77</v>
@@ -4780,13 +4822,13 @@
         <v>77</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -4837,7 +4879,7 @@
         <v>77</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -4846,7 +4888,7 @@
         <v>79</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>203</v>
+        <v>77</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>116</v>
@@ -4866,13 +4908,13 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D20" t="s" s="2">
         <v>77</v>
@@ -4894,13 +4936,13 @@
         <v>77</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4951,7 +4993,7 @@
         <v>77</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -4960,7 +5002,7 @@
         <v>79</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>203</v>
+        <v>77</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>116</v>
@@ -4980,13 +5022,13 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D21" t="s" s="2">
         <v>77</v>
@@ -5008,13 +5050,13 @@
         <v>77</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -5065,7 +5107,7 @@
         <v>77</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -5074,7 +5116,7 @@
         <v>79</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>203</v>
+        <v>77</v>
       </c>
       <c r="AJ21" t="s" s="2">
         <v>116</v>
@@ -5094,13 +5136,13 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="C22" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D22" t="s" s="2">
         <v>77</v>
@@ -5122,13 +5164,13 @@
         <v>77</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -5179,7 +5221,7 @@
         <v>77</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -5188,7 +5230,7 @@
         <v>79</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>203</v>
+        <v>77</v>
       </c>
       <c r="AJ22" t="s" s="2">
         <v>116</v>
@@ -5208,13 +5250,13 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="C23" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D23" t="s" s="2">
         <v>77</v>
@@ -5236,13 +5278,13 @@
         <v>77</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -5293,7 +5335,7 @@
         <v>77</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -5302,7 +5344,7 @@
         <v>79</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>203</v>
+        <v>77</v>
       </c>
       <c r="AJ23" t="s" s="2">
         <v>116</v>
@@ -5322,13 +5364,13 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D24" t="s" s="2">
         <v>77</v>
@@ -5350,13 +5392,13 @@
         <v>77</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -5407,7 +5449,7 @@
         <v>77</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -5416,7 +5458,7 @@
         <v>79</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>203</v>
+        <v>77</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>116</v>
@@ -5436,10 +5478,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5465,16 +5507,16 @@
         <v>108</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="N25" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>77</v>
@@ -5511,19 +5553,19 @@
         <v>77</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="AC25" t="s" s="2">
-        <v>77</v>
+        <v>113</v>
       </c>
       <c r="AD25" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>77</v>
+        <v>114</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -5541,7 +5583,7 @@
         <v>77</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>77</v>
@@ -5552,10 +5594,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5578,13 +5620,13 @@
         <v>77</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -5623,10 +5665,10 @@
         <v>77</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AD26" t="s" s="2">
         <v>77</v>
@@ -5635,7 +5677,7 @@
         <v>141</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -5644,33 +5686,33 @@
         <v>79</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AJ26" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>77</v>
+        <v>244</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C27" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D27" t="s" s="2">
         <v>77</v>
@@ -5692,13 +5734,13 @@
         <v>77</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -5749,7 +5791,7 @@
         <v>77</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -5758,33 +5800,33 @@
         <v>79</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AJ27" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>77</v>
+        <v>244</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C28" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="D28" t="s" s="2">
         <v>77</v>
@@ -5806,13 +5848,13 @@
         <v>77</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -5863,7 +5905,7 @@
         <v>77</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -5872,30 +5914,30 @@
         <v>79</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>77</v>
+        <v>244</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -6004,10 +6046,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6118,10 +6160,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6144,19 +6186,19 @@
         <v>88</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>77</v>
@@ -6181,13 +6223,13 @@
         <v>77</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>77</v>
@@ -6205,7 +6247,7 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -6223,21 +6265,21 @@
         <v>77</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>192</v>
+        <v>195</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6260,19 +6302,19 @@
         <v>88</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>77</v>
@@ -6300,10 +6342,10 @@
         <v>151</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>77</v>
@@ -6321,7 +6363,7 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -6330,7 +6372,7 @@
         <v>87</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AJ32" t="s" s="2">
         <v>99</v>
@@ -6339,21 +6381,21 @@
         <v>77</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6379,29 +6421,29 @@
         <v>129</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q33" s="2"/>
       <c r="R33" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="S33" t="s" s="2">
         <v>77</v>
       </c>
       <c r="T33" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="U33" t="s" s="2">
         <v>77</v>
@@ -6437,7 +6479,7 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -6455,21 +6497,21 @@
         <v>77</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6495,13 +6537,13 @@
         <v>101</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -6515,7 +6557,7 @@
         <v>77</v>
       </c>
       <c r="T34" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="U34" t="s" s="2">
         <v>77</v>
@@ -6551,7 +6593,7 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -6569,21 +6611,21 @@
         <v>77</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6606,15 +6648,17 @@
         <v>88</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="N35" s="2"/>
+        <v>304</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>305</v>
+      </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>77</v>
@@ -6663,7 +6707,7 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -6672,30 +6716,30 @@
         <v>87</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>99</v>
+        <v>307</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>305</v>
+        <v>309</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6718,16 +6762,16 @@
         <v>88</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -6777,7 +6821,7 @@
         <v>77</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -6786,33 +6830,33 @@
         <v>87</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>99</v>
+        <v>317</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>314</v>
+        <v>319</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C37" t="s" s="2">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="D37" t="s" s="2">
         <v>77</v>
@@ -6834,13 +6878,13 @@
         <v>77</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6891,7 +6935,7 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -6900,30 +6944,30 @@
         <v>79</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>77</v>
+        <v>244</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6946,17 +6990,19 @@
         <v>88</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="N38" s="2"/>
+        <v>326</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>327</v>
+      </c>
       <c r="O38" t="s" s="2">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>77</v>
@@ -7005,7 +7051,7 @@
         <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -7020,10 +7066,10 @@
         <v>99</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>77</v>
@@ -7034,10 +7080,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7063,14 +7109,16 @@
         <v>129</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="N39" s="2"/>
+        <v>332</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>333</v>
+      </c>
       <c r="O39" t="s" s="2">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>77</v>
@@ -7119,7 +7167,7 @@
         <v>77</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -7134,10 +7182,10 @@
         <v>99</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>77</v>
@@ -7148,10 +7196,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7174,15 +7222,17 @@
         <v>88</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>331</v>
+        <v>338</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="N40" s="2"/>
+        <v>339</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>340</v>
+      </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>77</v>
@@ -7231,7 +7281,7 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -7240,16 +7290,16 @@
         <v>79</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>99</v>
+        <v>317</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>77</v>
@@ -7260,10 +7310,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7286,17 +7336,17 @@
         <v>88</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" t="s" s="2">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>77</v>
@@ -7345,7 +7395,7 @@
         <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -7354,30 +7404,30 @@
         <v>87</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AJ41" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>77</v>
+        <v>244</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7400,19 +7450,19 @@
         <v>88</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>345</v>
+        <v>353</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>77</v>
@@ -7461,7 +7511,7 @@
         <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -7470,16 +7520,16 @@
         <v>79</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>99</v>
+        <v>317</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>348</v>
+        <v>356</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>77</v>
@@ -7490,10 +7540,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7516,17 +7566,17 @@
         <v>88</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>77</v>
@@ -7551,13 +7601,13 @@
         <v>77</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>77</v>
@@ -7575,7 +7625,7 @@
         <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>87</v>
@@ -7590,13 +7640,13 @@
         <v>99</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>77</v>
@@ -7604,10 +7654,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7630,16 +7680,16 @@
         <v>88</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7665,10 +7715,10 @@
         <v>77</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>361</v>
+        <v>369</v>
       </c>
       <c r="Z44" t="s" s="2">
         <v>77</v>
@@ -7689,7 +7739,7 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -7698,7 +7748,7 @@
         <v>87</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AJ44" t="s" s="2">
         <v>99</v>
@@ -7707,21 +7757,21 @@
         <v>77</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>362</v>
+        <v>370</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>77</v>
+        <v>371</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>363</v>
+        <v>372</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>363</v>
+        <v>372</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7744,17 +7794,19 @@
         <v>88</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>364</v>
+        <v>373</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="N45" s="2"/>
+        <v>374</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>375</v>
+      </c>
       <c r="O45" t="s" s="2">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>77</v>
@@ -7779,10 +7831,10 @@
         <v>77</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>367</v>
+        <v>377</v>
       </c>
       <c r="Z45" t="s" s="2">
         <v>77</v>
@@ -7803,7 +7855,7 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>363</v>
+        <v>372</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -7812,7 +7864,7 @@
         <v>87</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AJ45" t="s" s="2">
         <v>99</v>
@@ -7821,21 +7873,21 @@
         <v>77</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>368</v>
+        <v>378</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>77</v>
+        <v>371</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7858,16 +7910,16 @@
         <v>88</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>370</v>
+        <v>380</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>371</v>
+        <v>381</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>372</v>
+        <v>382</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7875,7 +7927,7 @@
       </c>
       <c r="Q46" s="2"/>
       <c r="R46" t="s" s="2">
-        <v>373</v>
+        <v>383</v>
       </c>
       <c r="S46" t="s" s="2">
         <v>77</v>
@@ -7893,13 +7945,13 @@
         <v>77</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>374</v>
+        <v>384</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>375</v>
+        <v>385</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>77</v>
@@ -7917,7 +7969,7 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>87</v>
@@ -7932,13 +7984,13 @@
         <v>99</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>376</v>
+        <v>386</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>378</v>
+        <v>388</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>77</v>
@@ -7946,10 +7998,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>379</v>
+        <v>389</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>379</v>
+        <v>389</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7972,23 +8024,23 @@
         <v>77</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>380</v>
+        <v>390</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>381</v>
+        <v>391</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" t="s" s="2">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q47" t="s" s="2">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="R47" t="s" s="2">
         <v>77</v>
@@ -8009,13 +8061,13 @@
         <v>77</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>384</v>
+        <v>394</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>77</v>
@@ -8033,7 +8085,7 @@
         <v>77</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>379</v>
+        <v>389</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -8048,13 +8100,13 @@
         <v>99</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>386</v>
+        <v>396</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>387</v>
+        <v>397</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>388</v>
+        <v>398</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>77</v>
@@ -8062,10 +8114,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>389</v>
+        <v>399</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>389</v>
+        <v>399</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8088,16 +8140,16 @@
         <v>88</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>390</v>
+        <v>400</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>391</v>
+        <v>401</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>392</v>
+        <v>402</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -8123,13 +8175,13 @@
         <v>77</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>394</v>
+        <v>404</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>77</v>
@@ -8147,7 +8199,7 @@
         <v>77</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>389</v>
+        <v>399</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -8156,30 +8208,30 @@
         <v>87</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>395</v>
+        <v>405</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>396</v>
+        <v>406</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>77</v>
+        <v>371</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8205,12 +8257,14 @@
         <v>101</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="N49" s="2"/>
+        <v>410</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>411</v>
+      </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>77</v>
@@ -8259,7 +8313,7 @@
         <v>77</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -8277,7 +8331,7 @@
         <v>77</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>401</v>
+        <v>412</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>77</v>
@@ -8288,10 +8342,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>402</v>
+        <v>413</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>402</v>
+        <v>413</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8314,19 +8368,19 @@
         <v>88</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>403</v>
+        <v>414</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>404</v>
+        <v>415</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>405</v>
+        <v>416</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>406</v>
+        <v>417</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>77</v>
@@ -8375,7 +8429,7 @@
         <v>77</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>402</v>
+        <v>413</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -8384,19 +8438,19 @@
         <v>87</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>99</v>
+        <v>317</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL50" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="AM50" t="s" s="2">
         <v>407</v>
-      </c>
-      <c r="AM50" t="s" s="2">
-        <v>397</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>77</v>
@@ -8404,14 +8458,14 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>408</v>
+        <v>419</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>408</v>
+        <v>419</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>409</v>
+        <v>420</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -8430,17 +8484,19 @@
         <v>88</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>410</v>
+        <v>421</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="N51" s="2"/>
+        <v>422</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>340</v>
+      </c>
       <c r="O51" t="s" s="2">
-        <v>412</v>
+        <v>423</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>77</v>
@@ -8489,7 +8545,7 @@
         <v>77</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>408</v>
+        <v>419</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -8498,19 +8554,19 @@
         <v>87</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>99</v>
+        <v>317</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>413</v>
+        <v>424</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>414</v>
+        <v>425</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>415</v>
+        <v>426</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>77</v>
@@ -8518,10 +8574,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>416</v>
+        <v>427</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>416</v>
+        <v>427</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8630,10 +8686,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>417</v>
+        <v>428</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>417</v>
+        <v>428</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8744,10 +8800,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>418</v>
+        <v>429</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>418</v>
+        <v>429</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8773,13 +8829,13 @@
         <v>101</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>419</v>
+        <v>430</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>420</v>
+        <v>431</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>421</v>
+        <v>432</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8829,7 +8885,7 @@
         <v>77</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>422</v>
+        <v>433</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -8838,7 +8894,7 @@
         <v>87</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>423</v>
+        <v>434</v>
       </c>
       <c r="AJ54" t="s" s="2">
         <v>99</v>
@@ -8847,7 +8903,7 @@
         <v>77</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>77</v>
@@ -8858,10 +8914,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>424</v>
+        <v>435</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>424</v>
+        <v>435</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8887,13 +8943,13 @@
         <v>129</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>425</v>
+        <v>436</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>426</v>
+        <v>437</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>427</v>
+        <v>438</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8922,10 +8978,10 @@
         <v>151</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>428</v>
+        <v>439</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>77</v>
@@ -8943,7 +8999,7 @@
         <v>77</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -8961,7 +9017,7 @@
         <v>77</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>77</v>
@@ -8972,10 +9028,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>431</v>
+        <v>442</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>431</v>
+        <v>442</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8998,16 +9054,16 @@
         <v>88</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>432</v>
+        <v>443</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>433</v>
+        <v>444</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>434</v>
+        <v>445</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>435</v>
+        <v>446</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -9057,7 +9113,7 @@
         <v>77</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>436</v>
+        <v>447</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -9066,7 +9122,7 @@
         <v>87</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>99</v>
@@ -9075,21 +9131,21 @@
         <v>77</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>437</v>
+        <v>448</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>77</v>
+        <v>244</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>438</v>
+        <v>449</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>438</v>
+        <v>449</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9115,13 +9171,13 @@
         <v>101</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>439</v>
+        <v>450</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>440</v>
+        <v>451</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>441</v>
+        <v>452</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -9171,7 +9227,7 @@
         <v>77</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>442</v>
+        <v>453</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -9189,7 +9245,7 @@
         <v>77</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>77</v>
@@ -9200,10 +9256,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>443</v>
+        <v>454</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>443</v>
+        <v>454</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9226,17 +9282,19 @@
         <v>88</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>444</v>
+        <v>455</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>445</v>
+        <v>456</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="N58" s="2"/>
+        <v>457</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>340</v>
+      </c>
       <c r="O58" t="s" s="2">
-        <v>447</v>
+        <v>458</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>77</v>
@@ -9285,7 +9343,7 @@
         <v>77</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>443</v>
+        <v>454</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -9294,19 +9352,19 @@
         <v>87</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>99</v>
+        <v>317</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>448</v>
+        <v>459</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>449</v>
+        <v>460</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>450</v>
+        <v>461</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>77</v>
@@ -9314,10 +9372,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>451</v>
+        <v>462</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>451</v>
+        <v>462</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9340,15 +9398,17 @@
         <v>88</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>452</v>
+        <v>463</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="N59" s="2"/>
+        <v>464</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>305</v>
+      </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>77</v>
@@ -9397,7 +9457,7 @@
         <v>77</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>451</v>
+        <v>462</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -9406,34 +9466,34 @@
         <v>87</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>99</v>
+        <v>307</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>454</v>
+        <v>465</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>455</v>
+        <v>466</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>456</v>
+        <v>467</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>77</v>
+        <v>468</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>457</v>
+        <v>469</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>457</v>
+        <v>469</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>458</v>
+        <v>470</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -9452,17 +9512,17 @@
         <v>77</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>459</v>
+        <v>471</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>460</v>
+        <v>472</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>461</v>
+        <v>473</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
-        <v>462</v>
+        <v>474</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>77</v>
@@ -9511,7 +9571,7 @@
         <v>77</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>457</v>
+        <v>469</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -9520,19 +9580,19 @@
         <v>87</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>463</v>
+        <v>475</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>464</v>
+        <v>476</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>465</v>
+        <v>477</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>466</v>
+        <v>478</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>77</v>
@@ -9540,14 +9600,14 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>467</v>
+        <v>479</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>467</v>
+        <v>479</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>468</v>
+        <v>480</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
@@ -9566,17 +9626,17 @@
         <v>88</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>459</v>
+        <v>471</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>469</v>
+        <v>481</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>470</v>
+        <v>482</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" t="s" s="2">
-        <v>471</v>
+        <v>483</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>77</v>
@@ -9625,7 +9685,7 @@
         <v>77</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>467</v>
+        <v>479</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -9634,7 +9694,7 @@
         <v>87</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>463</v>
+        <v>475</v>
       </c>
       <c r="AJ61" t="s" s="2">
         <v>99</v>
@@ -9643,7 +9703,7 @@
         <v>77</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>472</v>
+        <v>484</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>77</v>
@@ -9654,10 +9714,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>473</v>
+        <v>485</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>473</v>
+        <v>485</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9680,17 +9740,19 @@
         <v>88</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>474</v>
+        <v>486</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>475</v>
+        <v>487</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>476</v>
-      </c>
-      <c r="N62" s="2"/>
+        <v>488</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>340</v>
+      </c>
       <c r="O62" t="s" s="2">
-        <v>477</v>
+        <v>489</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>77</v>
@@ -9739,7 +9801,7 @@
         <v>77</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>473</v>
+        <v>485</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -9748,19 +9810,19 @@
         <v>87</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>99</v>
+        <v>317</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>478</v>
+        <v>490</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>479</v>
+        <v>491</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>480</v>
+        <v>492</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>77</v>
@@ -9768,10 +9830,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>481</v>
+        <v>493</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>481</v>
+        <v>493</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9794,17 +9856,19 @@
         <v>77</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>482</v>
+        <v>494</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="N63" s="2"/>
+        <v>495</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>375</v>
+      </c>
       <c r="O63" t="s" s="2">
-        <v>484</v>
+        <v>496</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>77</v>
@@ -9829,13 +9893,13 @@
         <v>77</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>485</v>
+        <v>497</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>486</v>
+        <v>498</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>77</v>
@@ -9853,7 +9917,7 @@
         <v>77</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>481</v>
+        <v>493</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -9862,30 +9926,30 @@
         <v>79</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AJ63" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>487</v>
+        <v>499</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>488</v>
+        <v>500</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>489</v>
+        <v>501</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>77</v>
+        <v>371</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>490</v>
+        <v>502</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>490</v>
+        <v>502</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9994,10 +10058,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>491</v>
+        <v>503</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>491</v>
+        <v>503</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10108,10 +10172,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>492</v>
+        <v>504</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>492</v>
+        <v>504</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10137,16 +10201,16 @@
         <v>147</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>493</v>
+        <v>505</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>494</v>
+        <v>506</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>495</v>
+        <v>507</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>496</v>
+        <v>508</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>77</v>
@@ -10171,11 +10235,11 @@
         <v>77</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Y66" s="2"/>
       <c r="Z66" t="s" s="2">
-        <v>497</v>
+        <v>509</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>77</v>
@@ -10193,7 +10257,7 @@
         <v>77</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>498</v>
+        <v>510</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
@@ -10202,7 +10266,7 @@
         <v>79</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AJ66" t="s" s="2">
         <v>99</v>
@@ -10211,21 +10275,21 @@
         <v>77</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>499</v>
+        <v>511</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>500</v>
+        <v>512</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>501</v>
+        <v>513</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>501</v>
+        <v>513</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10251,16 +10315,16 @@
         <v>101</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>502</v>
+        <v>514</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>503</v>
+        <v>515</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>504</v>
+        <v>516</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>505</v>
+        <v>517</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>77</v>
@@ -10309,7 +10373,7 @@
         <v>77</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>506</v>
+        <v>518</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
@@ -10327,25 +10391,25 @@
         <v>77</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>507</v>
+        <v>519</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>508</v>
+        <v>520</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>509</v>
+        <v>521</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>509</v>
+        <v>521</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>510</v>
+        <v>522</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
@@ -10364,19 +10428,19 @@
         <v>88</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>511</v>
+        <v>523</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>512</v>
+        <v>524</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>513</v>
+        <v>525</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>514</v>
+        <v>526</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>515</v>
+        <v>527</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>77</v>
@@ -10425,7 +10489,7 @@
         <v>77</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>509</v>
+        <v>521</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
@@ -10434,19 +10498,19 @@
         <v>87</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>99</v>
+        <v>317</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>516</v>
+        <v>528</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>517</v>
+        <v>529</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>489</v>
+        <v>501</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>77</v>
@@ -10454,10 +10518,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>518</v>
+        <v>530</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>518</v>
+        <v>530</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10480,17 +10544,19 @@
         <v>88</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>519</v>
+        <v>531</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>520</v>
+        <v>532</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="N69" s="2"/>
+        <v>533</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>340</v>
+      </c>
       <c r="O69" t="s" s="2">
-        <v>522</v>
+        <v>534</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>77</v>
@@ -10539,7 +10605,7 @@
         <v>77</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>518</v>
+        <v>530</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
@@ -10548,19 +10614,19 @@
         <v>87</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>99</v>
+        <v>317</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>523</v>
+        <v>535</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>524</v>
+        <v>536</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>525</v>
+        <v>537</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>77</v>
@@ -10568,10 +10634,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>526</v>
+        <v>538</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>526</v>
+        <v>538</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10594,16 +10660,16 @@
         <v>77</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>527</v>
+        <v>539</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>528</v>
+        <v>540</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>529</v>
+        <v>541</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -10629,10 +10695,10 @@
         <v>77</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>530</v>
+        <v>542</v>
       </c>
       <c r="Z70" t="s" s="2">
         <v>77</v>
@@ -10653,7 +10719,7 @@
         <v>77</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>526</v>
+        <v>538</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
@@ -10662,30 +10728,30 @@
         <v>87</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>531</v>
+        <v>543</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>532</v>
+        <v>544</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>533</v>
+        <v>545</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>534</v>
+        <v>546</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>535</v>
+        <v>547</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>535</v>
+        <v>547</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10708,16 +10774,16 @@
         <v>77</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>527</v>
+        <v>539</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>536</v>
+        <v>548</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>537</v>
+        <v>549</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10767,7 +10833,7 @@
         <v>77</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>535</v>
+        <v>547</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
@@ -10776,19 +10842,19 @@
         <v>87</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>99</v>
+        <v>317</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>538</v>
+        <v>550</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>539</v>
+        <v>551</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>533</v>
+        <v>545</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>77</v>
@@ -10796,10 +10862,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>540</v>
+        <v>552</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>540</v>
+        <v>552</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10822,15 +10888,17 @@
         <v>77</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>541</v>
+        <v>553</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>542</v>
+        <v>554</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>543</v>
-      </c>
-      <c r="N72" s="2"/>
+        <v>555</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>340</v>
+      </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>77</v>
@@ -10879,7 +10947,7 @@
         <v>77</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>540</v>
+        <v>552</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>78</v>
@@ -10888,30 +10956,30 @@
         <v>79</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>99</v>
+        <v>317</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>544</v>
+        <v>556</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>545</v>
+        <v>557</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>546</v>
+        <v>558</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>547</v>
+        <v>559</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>547</v>
+        <v>559</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10934,15 +11002,17 @@
         <v>77</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>548</v>
+        <v>560</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>549</v>
+        <v>561</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>550</v>
-      </c>
-      <c r="N73" s="2"/>
+        <v>562</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>563</v>
+      </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>77</v>
@@ -10991,7 +11061,7 @@
         <v>77</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>547</v>
+        <v>559</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
@@ -11000,34 +11070,34 @@
         <v>79</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AJ73" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>551</v>
+        <v>564</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>552</v>
+        <v>565</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>77</v>
+        <v>195</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>553</v>
+        <v>566</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>553</v>
+        <v>566</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>554</v>
+        <v>567</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -11046,16 +11116,16 @@
         <v>77</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>555</v>
+        <v>568</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>556</v>
+        <v>569</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>557</v>
+        <v>570</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>558</v>
+        <v>571</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -11105,7 +11175,7 @@
         <v>77</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>553</v>
+        <v>566</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
@@ -11114,16 +11184,16 @@
         <v>79</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>99</v>
+        <v>317</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>560</v>
+        <v>573</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>77</v>
@@ -11134,10 +11204,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>561</v>
+        <v>574</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>561</v>
+        <v>574</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11160,17 +11230,17 @@
         <v>77</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>562</v>
+        <v>575</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>563</v>
+        <v>576</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>564</v>
+        <v>577</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" t="s" s="2">
-        <v>565</v>
+        <v>578</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>77</v>
@@ -11219,7 +11289,7 @@
         <v>77</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>561</v>
+        <v>574</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>
@@ -11228,7 +11298,7 @@
         <v>87</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AJ75" t="s" s="2">
         <v>99</v>
@@ -11237,7 +11307,7 @@
         <v>77</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>566</v>
+        <v>579</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>77</v>
@@ -11248,10 +11318,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>567</v>
+        <v>580</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>567</v>
+        <v>580</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11360,10 +11430,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>568</v>
+        <v>581</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>568</v>
+        <v>581</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11433,16 +11503,16 @@
         <v>77</v>
       </c>
       <c r="AB77" t="s" s="2">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="AC77" t="s" s="2">
-        <v>77</v>
+        <v>113</v>
       </c>
       <c r="AD77" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE77" t="s" s="2">
-        <v>77</v>
+        <v>114</v>
       </c>
       <c r="AF77" t="s" s="2">
         <v>115</v>
@@ -11474,14 +11544,14 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>569</v>
+        <v>582</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>569</v>
+        <v>582</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>570</v>
+        <v>583</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
@@ -11503,16 +11573,16 @@
         <v>108</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>571</v>
+        <v>584</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>572</v>
+        <v>585</v>
       </c>
       <c r="N78" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>77</v>
@@ -11561,7 +11631,7 @@
         <v>77</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>573</v>
+        <v>586</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
@@ -11579,7 +11649,7 @@
         <v>77</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="AM78" t="s" s="2">
         <v>77</v>
@@ -11590,10 +11660,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>574</v>
+        <v>587</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>574</v>
+        <v>587</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11616,17 +11686,17 @@
         <v>77</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>575</v>
+        <v>588</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>576</v>
+        <v>589</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>577</v>
+        <v>590</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" t="s" s="2">
-        <v>578</v>
+        <v>591</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>77</v>
@@ -11675,7 +11745,7 @@
         <v>77</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>574</v>
+        <v>587</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>78</v>
@@ -11693,7 +11763,7 @@
         <v>77</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>579</v>
+        <v>592</v>
       </c>
       <c r="AM79" t="s" s="2">
         <v>77</v>
@@ -11704,10 +11774,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>580</v>
+        <v>593</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>580</v>
+        <v>593</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11730,19 +11800,19 @@
         <v>77</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>581</v>
+        <v>594</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>582</v>
+        <v>595</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>583</v>
+        <v>596</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>584</v>
+        <v>597</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>77</v>
@@ -11791,7 +11861,7 @@
         <v>77</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>580</v>
+        <v>593</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>78</v>
@@ -11800,30 +11870,30 @@
         <v>87</v>
       </c>
       <c r="AI80" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>99</v>
+        <v>307</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>585</v>
+        <v>598</v>
       </c>
       <c r="AM80" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>77</v>
+        <v>468</v>
       </c>
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>586</v>
+        <v>599</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>586</v>
+        <v>599</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11846,15 +11916,17 @@
         <v>77</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>587</v>
+        <v>600</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>588</v>
+        <v>601</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>589</v>
-      </c>
-      <c r="N81" s="2"/>
+        <v>602</v>
+      </c>
+      <c r="N81" t="s" s="2">
+        <v>340</v>
+      </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
         <v>77</v>
@@ -11903,7 +11975,7 @@
         <v>77</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>586</v>
+        <v>599</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>78</v>
@@ -11912,16 +11984,16 @@
         <v>79</v>
       </c>
       <c r="AI81" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>99</v>
+        <v>317</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>590</v>
+        <v>603</v>
       </c>
       <c r="AM81" t="s" s="2">
         <v>77</v>
@@ -11932,14 +12004,14 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>591</v>
+        <v>604</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>591</v>
+        <v>604</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>592</v>
+        <v>605</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
@@ -11958,17 +12030,17 @@
         <v>77</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>562</v>
+        <v>575</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>593</v>
+        <v>606</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>594</v>
+        <v>607</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" t="s" s="2">
-        <v>595</v>
+        <v>608</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>77</v>
@@ -12005,7 +12077,7 @@
         <v>77</v>
       </c>
       <c r="AB82" t="s" s="2">
-        <v>596</v>
+        <v>609</v>
       </c>
       <c r="AC82" s="2"/>
       <c r="AD82" t="s" s="2">
@@ -12015,7 +12087,7 @@
         <v>141</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>591</v>
+        <v>604</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>78</v>
@@ -12024,7 +12096,7 @@
         <v>79</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AJ82" t="s" s="2">
         <v>99</v>
@@ -12033,7 +12105,7 @@
         <v>77</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>597</v>
+        <v>610</v>
       </c>
       <c r="AM82" t="s" s="2">
         <v>77</v>
@@ -12044,10 +12116,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>598</v>
+        <v>611</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>598</v>
+        <v>611</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12156,10 +12228,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>599</v>
+        <v>612</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>599</v>
+        <v>612</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12229,16 +12301,16 @@
         <v>77</v>
       </c>
       <c r="AB84" t="s" s="2">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="AC84" t="s" s="2">
-        <v>77</v>
+        <v>113</v>
       </c>
       <c r="AD84" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE84" t="s" s="2">
-        <v>77</v>
+        <v>114</v>
       </c>
       <c r="AF84" t="s" s="2">
         <v>115</v>
@@ -12270,14 +12342,14 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>600</v>
+        <v>613</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>600</v>
+        <v>613</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>570</v>
+        <v>583</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
@@ -12299,16 +12371,16 @@
         <v>108</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>571</v>
+        <v>584</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>572</v>
+        <v>585</v>
       </c>
       <c r="N85" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O85" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>77</v>
@@ -12357,7 +12429,7 @@
         <v>77</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>573</v>
+        <v>586</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>78</v>
@@ -12375,7 +12447,7 @@
         <v>77</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="AM85" t="s" s="2">
         <v>77</v>
@@ -12386,14 +12458,14 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>601</v>
+        <v>614</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>601</v>
+        <v>614</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
-        <v>602</v>
+        <v>615</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
@@ -12412,19 +12484,19 @@
         <v>77</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>603</v>
+        <v>616</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>604</v>
+        <v>617</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>605</v>
+        <v>618</v>
       </c>
       <c r="O86" t="s" s="2">
-        <v>606</v>
+        <v>619</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>77</v>
@@ -12449,10 +12521,10 @@
         <v>77</v>
       </c>
       <c r="X86" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="Y86" t="s" s="2">
-        <v>607</v>
+        <v>620</v>
       </c>
       <c r="Z86" t="s" s="2">
         <v>77</v>
@@ -12473,7 +12545,7 @@
         <v>77</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>601</v>
+        <v>614</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>87</v>
@@ -12482,7 +12554,7 @@
         <v>87</v>
       </c>
       <c r="AI86" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AJ86" t="s" s="2">
         <v>99</v>
@@ -12491,21 +12563,21 @@
         <v>77</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>597</v>
+        <v>610</v>
       </c>
       <c r="AM86" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>77</v>
+        <v>371</v>
       </c>
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>608</v>
+        <v>621</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>608</v>
+        <v>621</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12528,13 +12600,13 @@
         <v>77</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>609</v>
+        <v>622</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>610</v>
+        <v>623</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>611</v>
+        <v>624</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -12585,7 +12657,7 @@
         <v>77</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>608</v>
+        <v>621</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>87</v>
@@ -12594,7 +12666,7 @@
         <v>87</v>
       </c>
       <c r="AI87" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AJ87" t="s" s="2">
         <v>99</v>
@@ -12603,7 +12675,7 @@
         <v>77</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>597</v>
+        <v>610</v>
       </c>
       <c r="AM87" t="s" s="2">
         <v>77</v>
@@ -12614,16 +12686,16 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>612</v>
+        <v>625</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>591</v>
+        <v>604</v>
       </c>
       <c r="C88" t="s" s="2">
-        <v>613</v>
+        <v>626</v>
       </c>
       <c r="D88" t="s" s="2">
-        <v>592</v>
+        <v>605</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
@@ -12642,17 +12714,17 @@
         <v>77</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>562</v>
+        <v>575</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>614</v>
+        <v>627</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>615</v>
+        <v>628</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" t="s" s="2">
-        <v>595</v>
+        <v>608</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>77</v>
@@ -12701,7 +12773,7 @@
         <v>77</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>591</v>
+        <v>604</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>78</v>
@@ -12710,7 +12782,7 @@
         <v>79</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AJ88" t="s" s="2">
         <v>99</v>
@@ -12719,7 +12791,7 @@
         <v>77</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>597</v>
+        <v>610</v>
       </c>
       <c r="AM88" t="s" s="2">
         <v>77</v>
@@ -12730,10 +12802,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>616</v>
+        <v>629</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>598</v>
+        <v>611</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12842,10 +12914,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>617</v>
+        <v>630</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>599</v>
+        <v>612</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12915,16 +12987,16 @@
         <v>77</v>
       </c>
       <c r="AB90" t="s" s="2">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="AC90" t="s" s="2">
-        <v>77</v>
+        <v>113</v>
       </c>
       <c r="AD90" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE90" t="s" s="2">
-        <v>77</v>
+        <v>114</v>
       </c>
       <c r="AF90" t="s" s="2">
         <v>115</v>
@@ -12956,14 +13028,14 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>618</v>
+        <v>631</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>600</v>
+        <v>613</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>570</v>
+        <v>583</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
@@ -12985,16 +13057,16 @@
         <v>108</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>571</v>
+        <v>584</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>572</v>
+        <v>585</v>
       </c>
       <c r="N91" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>77</v>
@@ -13043,7 +13115,7 @@
         <v>77</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>573</v>
+        <v>586</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>78</v>
@@ -13061,7 +13133,7 @@
         <v>77</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="AM91" t="s" s="2">
         <v>77</v>
@@ -13072,14 +13144,14 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>619</v>
+        <v>632</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>601</v>
+        <v>614</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
-        <v>602</v>
+        <v>615</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
@@ -13098,19 +13170,19 @@
         <v>77</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>603</v>
+        <v>616</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>604</v>
+        <v>617</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>605</v>
+        <v>618</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>606</v>
+        <v>619</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>77</v>
@@ -13135,10 +13207,10 @@
         <v>77</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>607</v>
+        <v>620</v>
       </c>
       <c r="Z92" t="s" s="2">
         <v>77</v>
@@ -13159,7 +13231,7 @@
         <v>77</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>601</v>
+        <v>614</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>87</v>
@@ -13168,7 +13240,7 @@
         <v>87</v>
       </c>
       <c r="AI92" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AJ92" t="s" s="2">
         <v>99</v>
@@ -13177,21 +13249,21 @@
         <v>77</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>597</v>
+        <v>610</v>
       </c>
       <c r="AM92" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>77</v>
+        <v>371</v>
       </c>
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>620</v>
+        <v>633</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>621</v>
+        <v>634</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13300,10 +13372,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>622</v>
+        <v>635</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>623</v>
+        <v>636</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13414,10 +13486,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>624</v>
+        <v>637</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>625</v>
+        <v>638</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13443,16 +13515,16 @@
         <v>147</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>493</v>
+        <v>505</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>494</v>
+        <v>506</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>495</v>
+        <v>507</v>
       </c>
       <c r="O95" t="s" s="2">
-        <v>496</v>
+        <v>508</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>77</v>
@@ -13477,11 +13549,11 @@
         <v>77</v>
       </c>
       <c r="X95" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Y95" s="2"/>
       <c r="Z95" t="s" s="2">
-        <v>626</v>
+        <v>639</v>
       </c>
       <c r="AA95" t="s" s="2">
         <v>77</v>
@@ -13499,7 +13571,7 @@
         <v>77</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>498</v>
+        <v>510</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>78</v>
@@ -13508,7 +13580,7 @@
         <v>79</v>
       </c>
       <c r="AI95" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AJ95" t="s" s="2">
         <v>99</v>
@@ -13517,21 +13589,21 @@
         <v>77</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>499</v>
+        <v>511</v>
       </c>
       <c r="AM95" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>500</v>
+        <v>512</v>
       </c>
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>627</v>
+        <v>640</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>628</v>
+        <v>641</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13640,10 +13712,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>629</v>
+        <v>642</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>630</v>
+        <v>643</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13754,10 +13826,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>631</v>
+        <v>644</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>632</v>
+        <v>645</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13783,16 +13855,16 @@
         <v>129</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>633</v>
+        <v>646</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>634</v>
+        <v>647</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>635</v>
+        <v>648</v>
       </c>
       <c r="O98" t="s" s="2">
-        <v>636</v>
+        <v>649</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>77</v>
@@ -13841,7 +13913,7 @@
         <v>77</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>637</v>
+        <v>650</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>78</v>
@@ -13859,21 +13931,21 @@
         <v>77</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>638</v>
+        <v>651</v>
       </c>
       <c r="AM98" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>639</v>
+        <v>652</v>
       </c>
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>640</v>
+        <v>653</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>641</v>
+        <v>654</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13899,13 +13971,13 @@
         <v>101</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>642</v>
+        <v>655</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>643</v>
+        <v>656</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>644</v>
+        <v>657</v>
       </c>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
@@ -13955,7 +14027,7 @@
         <v>77</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>645</v>
+        <v>658</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>78</v>
@@ -13973,21 +14045,21 @@
         <v>77</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>646</v>
+        <v>659</v>
       </c>
       <c r="AM99" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>647</v>
+        <v>660</v>
       </c>
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>648</v>
+        <v>661</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>649</v>
+        <v>662</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14010,17 +14082,17 @@
         <v>88</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>650</v>
+        <v>663</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>651</v>
+        <v>664</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" t="s" s="2">
-        <v>652</v>
+        <v>665</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>77</v>
@@ -14069,7 +14141,7 @@
         <v>77</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>653</v>
+        <v>666</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>78</v>
@@ -14087,21 +14159,21 @@
         <v>77</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>654</v>
+        <v>667</v>
       </c>
       <c r="AM100" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>655</v>
+        <v>668</v>
       </c>
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>656</v>
+        <v>669</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>657</v>
+        <v>670</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14127,14 +14199,16 @@
         <v>101</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>658</v>
+        <v>671</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>659</v>
-      </c>
-      <c r="N101" s="2"/>
+        <v>672</v>
+      </c>
+      <c r="N101" t="s" s="2">
+        <v>411</v>
+      </c>
       <c r="O101" t="s" s="2">
-        <v>660</v>
+        <v>673</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>77</v>
@@ -14183,7 +14257,7 @@
         <v>77</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>661</v>
+        <v>674</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>78</v>
@@ -14201,21 +14275,21 @@
         <v>77</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>662</v>
+        <v>675</v>
       </c>
       <c r="AM101" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>663</v>
+        <v>676</v>
       </c>
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>664</v>
+        <v>677</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>665</v>
+        <v>678</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14238,19 +14312,19 @@
         <v>88</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>666</v>
+        <v>679</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>667</v>
+        <v>680</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>668</v>
+        <v>681</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>669</v>
+        <v>682</v>
       </c>
       <c r="O102" t="s" s="2">
-        <v>670</v>
+        <v>683</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>77</v>
@@ -14299,7 +14373,7 @@
         <v>77</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>671</v>
+        <v>684</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>78</v>
@@ -14317,21 +14391,21 @@
         <v>77</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>672</v>
+        <v>685</v>
       </c>
       <c r="AM102" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>673</v>
+        <v>686</v>
       </c>
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>674</v>
+        <v>687</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>675</v>
+        <v>688</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14357,16 +14431,16 @@
         <v>101</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>502</v>
+        <v>514</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>503</v>
+        <v>515</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>504</v>
+        <v>516</v>
       </c>
       <c r="O103" t="s" s="2">
-        <v>505</v>
+        <v>517</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>77</v>
@@ -14415,7 +14489,7 @@
         <v>77</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>506</v>
+        <v>518</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>78</v>
@@ -14433,21 +14507,21 @@
         <v>77</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>507</v>
+        <v>519</v>
       </c>
       <c r="AM103" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>508</v>
+        <v>520</v>
       </c>
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>676</v>
+        <v>689</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>608</v>
+        <v>621</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14470,13 +14544,13 @@
         <v>77</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>677</v>
+        <v>690</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>610</v>
+        <v>623</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>611</v>
+        <v>624</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -14527,7 +14601,7 @@
         <v>77</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>608</v>
+        <v>621</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>87</v>
@@ -14536,7 +14610,7 @@
         <v>87</v>
       </c>
       <c r="AI104" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AJ104" t="s" s="2">
         <v>99</v>
@@ -14545,7 +14619,7 @@
         <v>77</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>597</v>
+        <v>610</v>
       </c>
       <c r="AM104" t="s" s="2">
         <v>77</v>
@@ -14556,16 +14630,16 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>678</v>
+        <v>691</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>591</v>
+        <v>604</v>
       </c>
       <c r="C105" t="s" s="2">
-        <v>679</v>
+        <v>692</v>
       </c>
       <c r="D105" t="s" s="2">
-        <v>592</v>
+        <v>605</v>
       </c>
       <c r="E105" s="2"/>
       <c r="F105" t="s" s="2">
@@ -14584,17 +14658,17 @@
         <v>77</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>562</v>
+        <v>575</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>680</v>
+        <v>693</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>615</v>
+        <v>628</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" t="s" s="2">
-        <v>595</v>
+        <v>608</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>77</v>
@@ -14643,7 +14717,7 @@
         <v>77</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>591</v>
+        <v>604</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>78</v>
@@ -14652,7 +14726,7 @@
         <v>79</v>
       </c>
       <c r="AI105" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AJ105" t="s" s="2">
         <v>99</v>
@@ -14661,7 +14735,7 @@
         <v>77</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>597</v>
+        <v>610</v>
       </c>
       <c r="AM105" t="s" s="2">
         <v>77</v>
@@ -14672,10 +14746,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>681</v>
+        <v>694</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>598</v>
+        <v>611</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14784,10 +14858,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>682</v>
+        <v>695</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>599</v>
+        <v>612</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14857,16 +14931,16 @@
         <v>77</v>
       </c>
       <c r="AB107" t="s" s="2">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="AC107" t="s" s="2">
-        <v>77</v>
+        <v>113</v>
       </c>
       <c r="AD107" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE107" t="s" s="2">
-        <v>77</v>
+        <v>114</v>
       </c>
       <c r="AF107" t="s" s="2">
         <v>115</v>
@@ -14898,14 +14972,14 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>683</v>
+        <v>696</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>600</v>
+        <v>613</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
-        <v>570</v>
+        <v>583</v>
       </c>
       <c r="E108" s="2"/>
       <c r="F108" t="s" s="2">
@@ -14927,16 +15001,16 @@
         <v>108</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>571</v>
+        <v>584</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>572</v>
+        <v>585</v>
       </c>
       <c r="N108" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O108" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>77</v>
@@ -14985,7 +15059,7 @@
         <v>77</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>573</v>
+        <v>586</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>78</v>
@@ -15003,7 +15077,7 @@
         <v>77</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="AM108" t="s" s="2">
         <v>77</v>
@@ -15014,14 +15088,14 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>684</v>
+        <v>697</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>601</v>
+        <v>614</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
-        <v>602</v>
+        <v>615</v>
       </c>
       <c r="E109" s="2"/>
       <c r="F109" t="s" s="2">
@@ -15040,19 +15114,19 @@
         <v>77</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>603</v>
+        <v>616</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>604</v>
+        <v>617</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>605</v>
+        <v>618</v>
       </c>
       <c r="O109" t="s" s="2">
-        <v>606</v>
+        <v>619</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>77</v>
@@ -15077,10 +15151,10 @@
         <v>77</v>
       </c>
       <c r="X109" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="Y109" t="s" s="2">
-        <v>607</v>
+        <v>620</v>
       </c>
       <c r="Z109" t="s" s="2">
         <v>77</v>
@@ -15101,7 +15175,7 @@
         <v>77</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>601</v>
+        <v>614</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>87</v>
@@ -15110,7 +15184,7 @@
         <v>87</v>
       </c>
       <c r="AI109" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AJ109" t="s" s="2">
         <v>99</v>
@@ -15119,21 +15193,21 @@
         <v>77</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>597</v>
+        <v>610</v>
       </c>
       <c r="AM109" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN109" t="s" s="2">
-        <v>77</v>
+        <v>371</v>
       </c>
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>685</v>
+        <v>698</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>621</v>
+        <v>634</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15242,10 +15316,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>686</v>
+        <v>699</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>623</v>
+        <v>636</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15356,10 +15430,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>687</v>
+        <v>700</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>625</v>
+        <v>638</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15385,16 +15459,16 @@
         <v>147</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>493</v>
+        <v>505</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>494</v>
+        <v>506</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>495</v>
+        <v>507</v>
       </c>
       <c r="O112" t="s" s="2">
-        <v>496</v>
+        <v>508</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>77</v>
@@ -15419,11 +15493,11 @@
         <v>77</v>
       </c>
       <c r="X112" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Y112" s="2"/>
       <c r="Z112" t="s" s="2">
-        <v>626</v>
+        <v>639</v>
       </c>
       <c r="AA112" t="s" s="2">
         <v>77</v>
@@ -15441,7 +15515,7 @@
         <v>77</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>498</v>
+        <v>510</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>78</v>
@@ -15450,7 +15524,7 @@
         <v>79</v>
       </c>
       <c r="AI112" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AJ112" t="s" s="2">
         <v>99</v>
@@ -15459,21 +15533,21 @@
         <v>77</v>
       </c>
       <c r="AL112" t="s" s="2">
-        <v>499</v>
+        <v>511</v>
       </c>
       <c r="AM112" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN112" t="s" s="2">
-        <v>500</v>
+        <v>512</v>
       </c>
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>688</v>
+        <v>701</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>628</v>
+        <v>641</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15582,10 +15656,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>689</v>
+        <v>702</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>630</v>
+        <v>643</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15696,10 +15770,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>690</v>
+        <v>703</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>632</v>
+        <v>645</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -15725,16 +15799,16 @@
         <v>129</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>633</v>
+        <v>646</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>634</v>
+        <v>647</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>635</v>
+        <v>648</v>
       </c>
       <c r="O115" t="s" s="2">
-        <v>636</v>
+        <v>649</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>77</v>
@@ -15783,7 +15857,7 @@
         <v>77</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>637</v>
+        <v>650</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>78</v>
@@ -15801,21 +15875,21 @@
         <v>77</v>
       </c>
       <c r="AL115" t="s" s="2">
-        <v>638</v>
+        <v>651</v>
       </c>
       <c r="AM115" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN115" t="s" s="2">
-        <v>639</v>
+        <v>652</v>
       </c>
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>691</v>
+        <v>704</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>641</v>
+        <v>654</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -15841,13 +15915,13 @@
         <v>101</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>642</v>
+        <v>655</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>643</v>
+        <v>656</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>644</v>
+        <v>657</v>
       </c>
       <c r="O116" s="2"/>
       <c r="P116" t="s" s="2">
@@ -15897,7 +15971,7 @@
         <v>77</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>645</v>
+        <v>658</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>78</v>
@@ -15915,21 +15989,21 @@
         <v>77</v>
       </c>
       <c r="AL116" t="s" s="2">
-        <v>646</v>
+        <v>659</v>
       </c>
       <c r="AM116" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN116" t="s" s="2">
-        <v>647</v>
+        <v>660</v>
       </c>
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>692</v>
+        <v>705</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>649</v>
+        <v>662</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -15952,24 +16026,24 @@
         <v>88</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>650</v>
+        <v>663</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>651</v>
+        <v>664</v>
       </c>
       <c r="N117" s="2"/>
       <c r="O117" t="s" s="2">
-        <v>652</v>
+        <v>665</v>
       </c>
       <c r="P117" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q117" s="2"/>
       <c r="R117" t="s" s="2">
-        <v>693</v>
+        <v>706</v>
       </c>
       <c r="S117" t="s" s="2">
         <v>77</v>
@@ -16011,7 +16085,7 @@
         <v>77</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>653</v>
+        <v>666</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>78</v>
@@ -16029,21 +16103,21 @@
         <v>77</v>
       </c>
       <c r="AL117" t="s" s="2">
-        <v>654</v>
+        <v>667</v>
       </c>
       <c r="AM117" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN117" t="s" s="2">
-        <v>655</v>
+        <v>668</v>
       </c>
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>694</v>
+        <v>707</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>657</v>
+        <v>670</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16069,14 +16143,16 @@
         <v>101</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>658</v>
+        <v>671</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>659</v>
-      </c>
-      <c r="N118" s="2"/>
+        <v>672</v>
+      </c>
+      <c r="N118" t="s" s="2">
+        <v>411</v>
+      </c>
       <c r="O118" t="s" s="2">
-        <v>660</v>
+        <v>673</v>
       </c>
       <c r="P118" t="s" s="2">
         <v>77</v>
@@ -16125,7 +16201,7 @@
         <v>77</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>661</v>
+        <v>674</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>78</v>
@@ -16143,21 +16219,21 @@
         <v>77</v>
       </c>
       <c r="AL118" t="s" s="2">
-        <v>662</v>
+        <v>675</v>
       </c>
       <c r="AM118" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN118" t="s" s="2">
-        <v>663</v>
+        <v>676</v>
       </c>
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>695</v>
+        <v>708</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>665</v>
+        <v>678</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16180,19 +16256,19 @@
         <v>88</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>666</v>
+        <v>679</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>667</v>
+        <v>680</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>668</v>
+        <v>681</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>669</v>
+        <v>682</v>
       </c>
       <c r="O119" t="s" s="2">
-        <v>670</v>
+        <v>683</v>
       </c>
       <c r="P119" t="s" s="2">
         <v>77</v>
@@ -16241,7 +16317,7 @@
         <v>77</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>671</v>
+        <v>684</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>78</v>
@@ -16259,21 +16335,21 @@
         <v>77</v>
       </c>
       <c r="AL119" t="s" s="2">
-        <v>672</v>
+        <v>685</v>
       </c>
       <c r="AM119" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN119" t="s" s="2">
-        <v>673</v>
+        <v>686</v>
       </c>
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>696</v>
+        <v>709</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>675</v>
+        <v>688</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16299,16 +16375,16 @@
         <v>101</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>502</v>
+        <v>514</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>503</v>
+        <v>515</v>
       </c>
       <c r="N120" t="s" s="2">
-        <v>504</v>
+        <v>516</v>
       </c>
       <c r="O120" t="s" s="2">
-        <v>505</v>
+        <v>517</v>
       </c>
       <c r="P120" t="s" s="2">
         <v>77</v>
@@ -16357,7 +16433,7 @@
         <v>77</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>506</v>
+        <v>518</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>78</v>
@@ -16375,21 +16451,21 @@
         <v>77</v>
       </c>
       <c r="AL120" t="s" s="2">
-        <v>507</v>
+        <v>519</v>
       </c>
       <c r="AM120" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN120" t="s" s="2">
-        <v>508</v>
+        <v>520</v>
       </c>
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>697</v>
+        <v>710</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>608</v>
+        <v>621</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16412,16 +16488,16 @@
         <v>77</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>698</v>
+        <v>711</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>610</v>
+        <v>623</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>611</v>
+        <v>624</v>
       </c>
       <c r="N121" t="s" s="2">
-        <v>699</v>
+        <v>712</v>
       </c>
       <c r="O121" s="2"/>
       <c r="P121" t="s" s="2">
@@ -16471,7 +16547,7 @@
         <v>77</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>608</v>
+        <v>621</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>87</v>
@@ -16480,7 +16556,7 @@
         <v>87</v>
       </c>
       <c r="AI121" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AJ121" t="s" s="2">
         <v>99</v>
@@ -16489,7 +16565,7 @@
         <v>77</v>
       </c>
       <c r="AL121" t="s" s="2">
-        <v>597</v>
+        <v>610</v>
       </c>
       <c r="AM121" t="s" s="2">
         <v>77</v>
@@ -16500,10 +16576,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>700</v>
+        <v>713</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>700</v>
+        <v>713</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -16526,17 +16602,17 @@
         <v>77</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>562</v>
+        <v>575</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>701</v>
+        <v>714</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>702</v>
+        <v>715</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" t="s" s="2">
-        <v>703</v>
+        <v>716</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>77</v>
@@ -16573,7 +16649,7 @@
         <v>77</v>
       </c>
       <c r="AB122" t="s" s="2">
-        <v>596</v>
+        <v>609</v>
       </c>
       <c r="AC122" s="2"/>
       <c r="AD122" t="s" s="2">
@@ -16583,7 +16659,7 @@
         <v>141</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>700</v>
+        <v>713</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>78</v>
@@ -16592,7 +16668,7 @@
         <v>79</v>
       </c>
       <c r="AI122" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AJ122" t="s" s="2">
         <v>99</v>
@@ -16601,7 +16677,7 @@
         <v>77</v>
       </c>
       <c r="AL122" t="s" s="2">
-        <v>597</v>
+        <v>610</v>
       </c>
       <c r="AM122" t="s" s="2">
         <v>77</v>
@@ -16612,10 +16688,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>704</v>
+        <v>717</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>704</v>
+        <v>717</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -16724,10 +16800,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>705</v>
+        <v>718</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>705</v>
+        <v>718</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -16797,16 +16873,16 @@
         <v>77</v>
       </c>
       <c r="AB124" t="s" s="2">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="AC124" t="s" s="2">
-        <v>77</v>
+        <v>113</v>
       </c>
       <c r="AD124" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE124" t="s" s="2">
-        <v>77</v>
+        <v>114</v>
       </c>
       <c r="AF124" t="s" s="2">
         <v>115</v>
@@ -16838,14 +16914,14 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>706</v>
+        <v>719</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>706</v>
+        <v>719</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
-        <v>570</v>
+        <v>583</v>
       </c>
       <c r="E125" s="2"/>
       <c r="F125" t="s" s="2">
@@ -16867,16 +16943,16 @@
         <v>108</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>571</v>
+        <v>584</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>572</v>
+        <v>585</v>
       </c>
       <c r="N125" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O125" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>77</v>
@@ -16925,7 +17001,7 @@
         <v>77</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>573</v>
+        <v>586</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>78</v>
@@ -16943,7 +17019,7 @@
         <v>77</v>
       </c>
       <c r="AL125" t="s" s="2">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="AM125" t="s" s="2">
         <v>77</v>
@@ -16954,14 +17030,14 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>707</v>
+        <v>720</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>707</v>
+        <v>720</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
-        <v>602</v>
+        <v>615</v>
       </c>
       <c r="E126" s="2"/>
       <c r="F126" t="s" s="2">
@@ -16980,17 +17056,19 @@
         <v>77</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>708</v>
+        <v>721</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>709</v>
-      </c>
-      <c r="N126" s="2"/>
+        <v>722</v>
+      </c>
+      <c r="N126" t="s" s="2">
+        <v>375</v>
+      </c>
       <c r="O126" t="s" s="2">
-        <v>710</v>
+        <v>723</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>77</v>
@@ -17015,10 +17093,10 @@
         <v>77</v>
       </c>
       <c r="X126" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="Y126" t="s" s="2">
-        <v>711</v>
+        <v>724</v>
       </c>
       <c r="Z126" t="s" s="2">
         <v>77</v>
@@ -17039,7 +17117,7 @@
         <v>77</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>707</v>
+        <v>720</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>87</v>
@@ -17048,7 +17126,7 @@
         <v>87</v>
       </c>
       <c r="AI126" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AJ126" t="s" s="2">
         <v>99</v>
@@ -17057,21 +17135,21 @@
         <v>77</v>
       </c>
       <c r="AL126" t="s" s="2">
-        <v>597</v>
+        <v>610</v>
       </c>
       <c r="AM126" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN126" t="s" s="2">
-        <v>77</v>
+        <v>371</v>
       </c>
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>712</v>
+        <v>725</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>712</v>
+        <v>725</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17094,17 +17172,17 @@
         <v>77</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>609</v>
+        <v>622</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>713</v>
+        <v>726</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>714</v>
+        <v>727</v>
       </c>
       <c r="N127" s="2"/>
       <c r="O127" t="s" s="2">
-        <v>715</v>
+        <v>728</v>
       </c>
       <c r="P127" t="s" s="2">
         <v>77</v>
@@ -17153,7 +17231,7 @@
         <v>77</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>712</v>
+        <v>725</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>87</v>
@@ -17162,7 +17240,7 @@
         <v>87</v>
       </c>
       <c r="AI127" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AJ127" t="s" s="2">
         <v>99</v>
@@ -17171,7 +17249,7 @@
         <v>77</v>
       </c>
       <c r="AL127" t="s" s="2">
-        <v>597</v>
+        <v>610</v>
       </c>
       <c r="AM127" t="s" s="2">
         <v>77</v>
@@ -17182,13 +17260,13 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>716</v>
+        <v>729</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>700</v>
+        <v>713</v>
       </c>
       <c r="C128" t="s" s="2">
-        <v>717</v>
+        <v>730</v>
       </c>
       <c r="D128" t="s" s="2">
         <v>77</v>
@@ -17210,17 +17288,17 @@
         <v>77</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>562</v>
+        <v>575</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>718</v>
+        <v>731</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>719</v>
+        <v>732</v>
       </c>
       <c r="N128" s="2"/>
       <c r="O128" t="s" s="2">
-        <v>703</v>
+        <v>716</v>
       </c>
       <c r="P128" t="s" s="2">
         <v>77</v>
@@ -17269,7 +17347,7 @@
         <v>77</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>700</v>
+        <v>713</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>78</v>
@@ -17278,7 +17356,7 @@
         <v>79</v>
       </c>
       <c r="AI128" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AJ128" t="s" s="2">
         <v>99</v>
@@ -17287,7 +17365,7 @@
         <v>77</v>
       </c>
       <c r="AL128" t="s" s="2">
-        <v>597</v>
+        <v>610</v>
       </c>
       <c r="AM128" t="s" s="2">
         <v>77</v>
@@ -17298,10 +17376,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>720</v>
+        <v>733</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>704</v>
+        <v>717</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17410,10 +17488,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>721</v>
+        <v>734</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>705</v>
+        <v>718</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -17483,16 +17561,16 @@
         <v>77</v>
       </c>
       <c r="AB130" t="s" s="2">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="AC130" t="s" s="2">
-        <v>77</v>
+        <v>113</v>
       </c>
       <c r="AD130" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE130" t="s" s="2">
-        <v>77</v>
+        <v>114</v>
       </c>
       <c r="AF130" t="s" s="2">
         <v>115</v>
@@ -17524,14 +17602,14 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>722</v>
+        <v>735</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>706</v>
+        <v>719</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
-        <v>570</v>
+        <v>583</v>
       </c>
       <c r="E131" s="2"/>
       <c r="F131" t="s" s="2">
@@ -17553,16 +17631,16 @@
         <v>108</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>571</v>
+        <v>584</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>572</v>
+        <v>585</v>
       </c>
       <c r="N131" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O131" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="P131" t="s" s="2">
         <v>77</v>
@@ -17611,7 +17689,7 @@
         <v>77</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>573</v>
+        <v>586</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>78</v>
@@ -17629,7 +17707,7 @@
         <v>77</v>
       </c>
       <c r="AL131" t="s" s="2">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="AM131" t="s" s="2">
         <v>77</v>
@@ -17640,14 +17718,14 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>723</v>
+        <v>736</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>707</v>
+        <v>720</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
-        <v>602</v>
+        <v>615</v>
       </c>
       <c r="E132" s="2"/>
       <c r="F132" t="s" s="2">
@@ -17666,17 +17744,19 @@
         <v>77</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>708</v>
+        <v>721</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>709</v>
-      </c>
-      <c r="N132" s="2"/>
+        <v>722</v>
+      </c>
+      <c r="N132" t="s" s="2">
+        <v>375</v>
+      </c>
       <c r="O132" t="s" s="2">
-        <v>710</v>
+        <v>723</v>
       </c>
       <c r="P132" t="s" s="2">
         <v>77</v>
@@ -17701,10 +17781,10 @@
         <v>77</v>
       </c>
       <c r="X132" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="Y132" t="s" s="2">
-        <v>711</v>
+        <v>724</v>
       </c>
       <c r="Z132" t="s" s="2">
         <v>77</v>
@@ -17725,7 +17805,7 @@
         <v>77</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>707</v>
+        <v>720</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>87</v>
@@ -17734,7 +17814,7 @@
         <v>87</v>
       </c>
       <c r="AI132" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AJ132" t="s" s="2">
         <v>99</v>
@@ -17743,21 +17823,21 @@
         <v>77</v>
       </c>
       <c r="AL132" t="s" s="2">
-        <v>597</v>
+        <v>610</v>
       </c>
       <c r="AM132" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN132" t="s" s="2">
-        <v>77</v>
+        <v>371</v>
       </c>
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>724</v>
+        <v>737</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>725</v>
+        <v>738</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -17866,10 +17946,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>726</v>
+        <v>739</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>727</v>
+        <v>740</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -17980,10 +18060,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>728</v>
+        <v>741</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>729</v>
+        <v>742</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -18009,16 +18089,16 @@
         <v>147</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>493</v>
+        <v>505</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>494</v>
+        <v>506</v>
       </c>
       <c r="N135" t="s" s="2">
-        <v>495</v>
+        <v>507</v>
       </c>
       <c r="O135" t="s" s="2">
-        <v>496</v>
+        <v>508</v>
       </c>
       <c r="P135" t="s" s="2">
         <v>77</v>
@@ -18043,11 +18123,11 @@
         <v>77</v>
       </c>
       <c r="X135" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Y135" s="2"/>
       <c r="Z135" t="s" s="2">
-        <v>626</v>
+        <v>639</v>
       </c>
       <c r="AA135" t="s" s="2">
         <v>77</v>
@@ -18065,7 +18145,7 @@
         <v>77</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>498</v>
+        <v>510</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>78</v>
@@ -18074,7 +18154,7 @@
         <v>79</v>
       </c>
       <c r="AI135" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AJ135" t="s" s="2">
         <v>99</v>
@@ -18083,21 +18163,21 @@
         <v>77</v>
       </c>
       <c r="AL135" t="s" s="2">
-        <v>499</v>
+        <v>511</v>
       </c>
       <c r="AM135" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN135" t="s" s="2">
-        <v>500</v>
+        <v>512</v>
       </c>
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>730</v>
+        <v>743</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>731</v>
+        <v>744</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -18206,10 +18286,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>732</v>
+        <v>745</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>733</v>
+        <v>746</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -18320,10 +18400,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>734</v>
+        <v>747</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>735</v>
+        <v>748</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -18349,16 +18429,16 @@
         <v>129</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>633</v>
+        <v>646</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>634</v>
+        <v>647</v>
       </c>
       <c r="N138" t="s" s="2">
-        <v>635</v>
+        <v>648</v>
       </c>
       <c r="O138" t="s" s="2">
-        <v>636</v>
+        <v>649</v>
       </c>
       <c r="P138" t="s" s="2">
         <v>77</v>
@@ -18407,7 +18487,7 @@
         <v>77</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>637</v>
+        <v>650</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>78</v>
@@ -18425,21 +18505,21 @@
         <v>77</v>
       </c>
       <c r="AL138" t="s" s="2">
-        <v>638</v>
+        <v>651</v>
       </c>
       <c r="AM138" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN138" t="s" s="2">
-        <v>639</v>
+        <v>652</v>
       </c>
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>736</v>
+        <v>749</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>737</v>
+        <v>750</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -18465,13 +18545,13 @@
         <v>101</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>642</v>
+        <v>655</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>643</v>
+        <v>656</v>
       </c>
       <c r="N139" t="s" s="2">
-        <v>644</v>
+        <v>657</v>
       </c>
       <c r="O139" s="2"/>
       <c r="P139" t="s" s="2">
@@ -18521,7 +18601,7 @@
         <v>77</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>645</v>
+        <v>658</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>78</v>
@@ -18539,21 +18619,21 @@
         <v>77</v>
       </c>
       <c r="AL139" t="s" s="2">
-        <v>646</v>
+        <v>659</v>
       </c>
       <c r="AM139" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN139" t="s" s="2">
-        <v>647</v>
+        <v>660</v>
       </c>
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>738</v>
+        <v>751</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>739</v>
+        <v>752</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -18576,24 +18656,24 @@
         <v>88</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>650</v>
+        <v>663</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>651</v>
+        <v>664</v>
       </c>
       <c r="N140" s="2"/>
       <c r="O140" t="s" s="2">
-        <v>652</v>
+        <v>665</v>
       </c>
       <c r="P140" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q140" s="2"/>
       <c r="R140" t="s" s="2">
-        <v>740</v>
+        <v>753</v>
       </c>
       <c r="S140" t="s" s="2">
         <v>77</v>
@@ -18635,7 +18715,7 @@
         <v>77</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>653</v>
+        <v>666</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>78</v>
@@ -18653,21 +18733,21 @@
         <v>77</v>
       </c>
       <c r="AL140" t="s" s="2">
-        <v>654</v>
+        <v>667</v>
       </c>
       <c r="AM140" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN140" t="s" s="2">
-        <v>655</v>
+        <v>668</v>
       </c>
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>741</v>
+        <v>754</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>742</v>
+        <v>755</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -18693,14 +18773,16 @@
         <v>101</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>658</v>
+        <v>671</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>659</v>
-      </c>
-      <c r="N141" s="2"/>
+        <v>672</v>
+      </c>
+      <c r="N141" t="s" s="2">
+        <v>411</v>
+      </c>
       <c r="O141" t="s" s="2">
-        <v>660</v>
+        <v>673</v>
       </c>
       <c r="P141" t="s" s="2">
         <v>77</v>
@@ -18749,7 +18831,7 @@
         <v>77</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>661</v>
+        <v>674</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>78</v>
@@ -18767,21 +18849,21 @@
         <v>77</v>
       </c>
       <c r="AL141" t="s" s="2">
-        <v>662</v>
+        <v>675</v>
       </c>
       <c r="AM141" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN141" t="s" s="2">
-        <v>663</v>
+        <v>676</v>
       </c>
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>743</v>
+        <v>756</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>744</v>
+        <v>757</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -18804,19 +18886,19 @@
         <v>88</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>666</v>
+        <v>679</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>667</v>
+        <v>680</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>668</v>
+        <v>681</v>
       </c>
       <c r="N142" t="s" s="2">
-        <v>669</v>
+        <v>682</v>
       </c>
       <c r="O142" t="s" s="2">
-        <v>670</v>
+        <v>683</v>
       </c>
       <c r="P142" t="s" s="2">
         <v>77</v>
@@ -18865,7 +18947,7 @@
         <v>77</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>671</v>
+        <v>684</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>78</v>
@@ -18883,21 +18965,21 @@
         <v>77</v>
       </c>
       <c r="AL142" t="s" s="2">
-        <v>672</v>
+        <v>685</v>
       </c>
       <c r="AM142" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN142" t="s" s="2">
-        <v>673</v>
+        <v>686</v>
       </c>
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>745</v>
+        <v>758</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>746</v>
+        <v>759</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -18923,16 +19005,16 @@
         <v>101</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>502</v>
+        <v>514</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>503</v>
+        <v>515</v>
       </c>
       <c r="N143" t="s" s="2">
-        <v>504</v>
+        <v>516</v>
       </c>
       <c r="O143" t="s" s="2">
-        <v>505</v>
+        <v>517</v>
       </c>
       <c r="P143" t="s" s="2">
         <v>77</v>
@@ -18981,7 +19063,7 @@
         <v>77</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>506</v>
+        <v>518</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>78</v>
@@ -18999,21 +19081,21 @@
         <v>77</v>
       </c>
       <c r="AL143" t="s" s="2">
-        <v>507</v>
+        <v>519</v>
       </c>
       <c r="AM143" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN143" t="s" s="2">
-        <v>508</v>
+        <v>520</v>
       </c>
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>747</v>
+        <v>760</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>712</v>
+        <v>725</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -19036,17 +19118,17 @@
         <v>77</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>748</v>
+        <v>761</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>713</v>
+        <v>726</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>714</v>
+        <v>727</v>
       </c>
       <c r="N144" s="2"/>
       <c r="O144" t="s" s="2">
-        <v>715</v>
+        <v>728</v>
       </c>
       <c r="P144" t="s" s="2">
         <v>77</v>
@@ -19095,7 +19177,7 @@
         <v>77</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>712</v>
+        <v>725</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>87</v>
@@ -19104,7 +19186,7 @@
         <v>87</v>
       </c>
       <c r="AI144" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AJ144" t="s" s="2">
         <v>99</v>
@@ -19113,7 +19195,7 @@
         <v>77</v>
       </c>
       <c r="AL144" t="s" s="2">
-        <v>597</v>
+        <v>610</v>
       </c>
       <c r="AM144" t="s" s="2">
         <v>77</v>

--- a/tiflow-core/develop/1.0.0-draft/StructureDefinition-GEM-ERP-PR-Task.xlsx
+++ b/tiflow-core/develop/1.0.0-draft/StructureDefinition-GEM-ERP-PR-Task.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5246" uniqueCount="762">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5226" uniqueCount="749">
   <si>
     <t>Property</t>
   </si>
@@ -499,163 +499,160 @@
     <t>Meta.security</t>
   </si>
   <si>
+    <t>Task.meta.tag</t>
+  </si>
+  <si>
+    <t>Tags applied to this resource</t>
+  </si>
+  <si>
+    <t>Tags applied to this resource. Tags are intended to be used to identify and relate resources to process and workflow, and applications are not required to consider the tags when interpreting the meaning of a resource.</t>
+  </si>
+  <si>
+    <t>The tags can be updated without changing the stated version of the resource. The list of tags is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
+  </si>
+  <si>
+    <t>example</t>
+  </si>
+  <si>
+    <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/common-tags|4.0.1</t>
+  </si>
+  <si>
+    <t>Meta.tag</t>
+  </si>
+  <si>
+    <t>Task.implicitRules</t>
+  </si>
+  <si>
+    <t>A set of rules under which this content was created</t>
+  </si>
+  <si>
+    <t>A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
+  </si>
+  <si>
+    <t>Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
+  </si>
+  <si>
+    <t>Resource.implicitRules</t>
+  </si>
+  <si>
+    <t>Task.language</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code
+</t>
+  </si>
+  <si>
+    <t>Language of the resource content</t>
+  </si>
+  <si>
+    <t>The base language in which the resource is written.</t>
+  </si>
+  <si>
+    <t>Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
+  </si>
+  <si>
+    <t>preferred</t>
+  </si>
+  <si>
+    <t>A human language.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
+  </si>
+  <si>
+    <t>Resource.language</t>
+  </si>
+  <si>
+    <t>Task.text</t>
+  </si>
+  <si>
+    <t>narrative
+htmlxhtmldisplay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Narrative
+</t>
+  </si>
+  <si>
+    <t>Text summary of the resource, for human interpretation</t>
+  </si>
+  <si>
+    <t>A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
+  </si>
+  <si>
+    <t>Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
+  </si>
+  <si>
+    <t>DomainResource.text</t>
+  </si>
+  <si>
+    <t>Act.text?</t>
+  </si>
+  <si>
+    <t>Task.contained</t>
+  </si>
+  <si>
+    <t>inline resources
+anonymous resourcescontained resources</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resource
+</t>
+  </si>
+  <si>
+    <t>Contained, inline Resources</t>
+  </si>
+  <si>
+    <t>These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
+  </si>
+  <si>
+    <t>This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
+  </si>
+  <si>
+    <t>DomainResource.contained</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Task.extension</t>
+  </si>
+  <si>
+    <t>Extension</t>
+  </si>
+  <si>
+    <t>An Extension</t>
+  </si>
+  <si>
+    <t>Erweiterungen für die Aufgabe, die durch url unterschieden werden.</t>
+  </si>
+  <si>
+    <t>DomainResource.extension</t>
+  </si>
+  <si>
+    <t>Task.extension:flowType</t>
+  </si>
+  <si>
+    <t>flowType</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://gematik.de/fhir/erp/StructureDefinition/GEM_ERP_EX_PrescriptionType}
+</t>
+  </si>
+  <si>
+    <t>Art der Verschreibung</t>
+  </si>
+  <si>
+    <t>Definiert den Typ des Rezepts. Das Codesystem enthält alle unterstützten Formulare.</t>
+  </si>
+  <si>
     <t xml:space="preserve">ele-1
 </t>
   </si>
   <si>
-    <t>CV</t>
-  </si>
-  <si>
-    <t>CE/CNE/CWE subset one of the sets of component 1-3 or 4-6</t>
-  </si>
-  <si>
-    <t>Task.meta.tag</t>
-  </si>
-  <si>
-    <t>Tags applied to this resource</t>
-  </si>
-  <si>
-    <t>Tags applied to this resource. Tags are intended to be used to identify and relate resources to process and workflow, and applications are not required to consider the tags when interpreting the meaning of a resource.</t>
-  </si>
-  <si>
-    <t>The tags can be updated without changing the stated version of the resource. The list of tags is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
-  </si>
-  <si>
-    <t>example</t>
-  </si>
-  <si>
-    <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/common-tags|4.0.1</t>
-  </si>
-  <si>
-    <t>Meta.tag</t>
-  </si>
-  <si>
-    <t>Task.implicitRules</t>
-  </si>
-  <si>
-    <t>A set of rules under which this content was created</t>
-  </si>
-  <si>
-    <t>A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
-  </si>
-  <si>
-    <t>Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
-  </si>
-  <si>
-    <t>Resource.implicitRules</t>
-  </si>
-  <si>
-    <t>Task.language</t>
-  </si>
-  <si>
-    <t xml:space="preserve">code
-</t>
-  </si>
-  <si>
-    <t>Language of the resource content</t>
-  </si>
-  <si>
-    <t>The base language in which the resource is written.</t>
-  </si>
-  <si>
-    <t>Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
-  </si>
-  <si>
-    <t>preferred</t>
-  </si>
-  <si>
-    <t>A human language.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
-  </si>
-  <si>
-    <t>Resource.language</t>
-  </si>
-  <si>
-    <t>Task.text</t>
-  </si>
-  <si>
-    <t>narrative
-htmlxhtmldisplay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Narrative
-</t>
-  </si>
-  <si>
-    <t>Text summary of the resource, for human interpretation</t>
-  </si>
-  <si>
-    <t>A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
-  </si>
-  <si>
-    <t>Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
-  </si>
-  <si>
-    <t>DomainResource.text</t>
-  </si>
-  <si>
-    <t>Act.text?</t>
-  </si>
-  <si>
-    <t>Task.contained</t>
-  </si>
-  <si>
-    <t>inline resources
-anonymous resourcescontained resources</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Resource
-</t>
-  </si>
-  <si>
-    <t>Contained, inline Resources</t>
-  </si>
-  <si>
-    <t>These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
-  </si>
-  <si>
-    <t>This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
-  </si>
-  <si>
-    <t>DomainResource.contained</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>Task.extension</t>
-  </si>
-  <si>
-    <t>Extension</t>
-  </si>
-  <si>
-    <t>An Extension</t>
-  </si>
-  <si>
-    <t>DomainResource.extension</t>
-  </si>
-  <si>
-    <t>Task.extension:flowType</t>
-  </si>
-  <si>
-    <t>flowType</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://gematik.de/fhir/erp/StructureDefinition/GEM_ERP_EX_PrescriptionType}
-</t>
-  </si>
-  <si>
-    <t>Art der Verschreibung</t>
-  </si>
-  <si>
-    <t>Definiert den Typ des Rezepts. Das Codesystem enthält alle unterstützten Formulare.</t>
-  </si>
-  <si>
     <t>Task.extension:acceptDate</t>
   </si>
   <si>
@@ -781,9 +778,6 @@
     <t>FiveWs.identifier</t>
   </si>
   <si>
-    <t>CX / EI (occasionally, more often EI maps to a resource id or a URL)</t>
-  </si>
-  <si>
     <t>Task.identifier:PrescriptionID</t>
   </si>
   <si>
@@ -967,15 +961,7 @@
     <t>Time period during which identifier is/was valid for use.</t>
   </si>
   <si>
-    <t>A Period specifies a range of time; the context of use will specify whether the entire range applies (e.g. "the patient was an inpatient of the hospital for this time range") or one value from the range applies (e.g. "give to the patient between these two times").
-Period is not used for a duration (a measure of elapsed time). See [Duration](http://hl7.org/fhir/R4/datatypes.html#Duration).</t>
-  </si>
-  <si>
     <t>Identifier.period</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-per-1:If present, start SHALL have a lower value than end {start.hasValue().not() or end.hasValue().not() or (start &lt;= end)}</t>
   </si>
   <si>
     <t>Role.effectiveTime or implied by context</t>
@@ -1006,10 +992,6 @@
     <t>Identifier.assigner</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
-  </si>
-  <si>
     <t>II.assigningAuthorityName but note that this is an improper use by the definition of the field.  Also Role.scoper</t>
   </si>
   <si>
@@ -1039,9 +1021,6 @@
     <t>The URL pointing to a *FHIR*-defined protocol, guideline, orderset or other definition that is adhered to in whole or in part by this Task.</t>
   </si>
   <si>
-    <t>see [Canonical References](http://hl7.org/fhir/R4/references.html#canonical)</t>
-  </si>
-  <si>
     <t>Enables a formal definition of how he task is to be performed, enabling automation.</t>
   </si>
   <si>
@@ -1055,9 +1034,6 @@
   </si>
   <si>
     <t>The URL pointing to an *externally* maintained  protocol, guideline, orderset or other definition that is adhered to in whole or in part by this Task.</t>
-  </si>
-  <si>
-    <t>see http://en.wikipedia.org/wiki/Uniform_resource_identifier</t>
   </si>
   <si>
     <t>Enables a formal definition of how he task is to be performed (e.g. using BPMN, BPEL, XPDL or other formal notation to be associated with a task), enabling automation.</t>
@@ -1079,9 +1055,6 @@
     <t>BasedOn refers to a higher-level authorization that triggered the creation of the task.  It references a "request" resource such as a ServiceRequest, MedicationRequest, ServiceRequest, CarePlan, etc. which is distinct from the "request" resource the task is seeking to fulfill.  This latter resource is referenced by FocusOn.  For example, based on a ServiceRequest (= BasedOn), a task is created to fulfill a procedureRequest ( = FocusOn ) to collect a specimen from a patient.</t>
   </si>
   <si>
-    <t>References SHALL be a reference to an actual FHIR resource, and SHALL be resolveable (allowing for access control, temporary unavailability, etc.). Resolution can be either by retrieval from the URL, or, where applicable by resource type, by treating an absolute reference as a canonical URL and looking it up in a local registry/repository.</t>
-  </si>
-  <si>
     <t>Request.basedOn, Event.basedOn</t>
   </si>
   <si>
@@ -1173,9 +1146,6 @@
     <t>.inboundRelationship[typeCode=SUBJ].source[classCode=CACT, moodCode=EVN, code="status change"].reasonCode</t>
   </si>
   <si>
-    <t>CE/CNE/CWE</t>
-  </si>
-  <si>
     <t>Task.businessStatus</t>
   </si>
   <si>
@@ -1183,9 +1153,6 @@
   </si>
   <si>
     <t>Contains business-specific nuances of the business state.</t>
-  </si>
-  <si>
-    <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.</t>
   </si>
   <si>
     <t>There's often a need to track substates of a task - this is often variable by specific workflow implementation.</t>
@@ -1292,9 +1259,6 @@
   </si>
   <si>
     <t>A free-text description of what is to be performed.</t>
-  </si>
-  <si>
-    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
   </si>
   <si>
     <t>.text</t>
@@ -1473,9 +1437,6 @@
     <t>FiveWs.done[x]</t>
   </si>
   <si>
-    <t>DR</t>
-  </si>
-  <si>
     <t>Task.authoredOn</t>
   </si>
   <si>
@@ -1766,9 +1727,6 @@
   </si>
   <si>
     <t>Free-text information captured about the task as it progresses.</t>
-  </si>
-  <si>
-    <t>For systems that do not have structured annotations, they can simply communicate a single annotation with no author or time.  This element may need to be included in narrative because of the potential for modifying information.  *Annotations SHOULD NOT* be used to communicate "modifying" information that could be computable. (This is a SHOULD because enforcing user behavior is nearly impossible).</t>
   </si>
   <si>
     <t>Request.note, Event.note</t>
@@ -2735,7 +2693,7 @@
     <col min="37" max="37" width="47.7734375" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="94.296875" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="31.65234375" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="53.91015625" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="39.109375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4092,7 +4050,7 @@
         <v>79</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>155</v>
+        <v>77</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>99</v>
@@ -4101,21 +4059,21 @@
         <v>77</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>156</v>
+        <v>77</v>
       </c>
       <c r="AM12" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>157</v>
+        <v>77</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -4141,13 +4099,13 @@
         <v>147</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -4173,31 +4131,31 @@
         <v>77</v>
       </c>
       <c r="X13" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="Y13" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="Z13" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="AA13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF13" t="s" s="2">
         <v>162</v>
-      </c>
-      <c r="Y13" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="Z13" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="AA13" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB13" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC13" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD13" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE13" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF13" t="s" s="2">
-        <v>165</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>78</v>
@@ -4206,7 +4164,7 @@
         <v>79</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>155</v>
+        <v>77</v>
       </c>
       <c r="AJ13" t="s" s="2">
         <v>99</v>
@@ -4215,21 +4173,21 @@
         <v>77</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>156</v>
+        <v>77</v>
       </c>
       <c r="AM13" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>157</v>
+        <v>77</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -4255,13 +4213,13 @@
         <v>129</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -4311,7 +4269,7 @@
         <v>77</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
@@ -4340,10 +4298,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -4366,16 +4324,16 @@
         <v>77</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="L15" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="M15" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="N15" t="s" s="2">
         <v>172</v>
-      </c>
-      <c r="L15" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>175</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -4401,31 +4359,31 @@
         <v>77</v>
       </c>
       <c r="X15" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="Y15" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="Z15" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="AA15" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB15" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC15" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD15" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE15" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF15" t="s" s="2">
         <v>176</v>
-      </c>
-      <c r="Y15" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="Z15" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="AA15" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB15" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC15" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD15" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE15" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF15" t="s" s="2">
-        <v>179</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
@@ -4454,14 +4412,14 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -4480,16 +4438,16 @@
         <v>77</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="L16" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="M16" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="N16" t="s" s="2">
         <v>182</v>
-      </c>
-      <c r="L16" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="M16" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>185</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -4539,7 +4497,7 @@
         <v>77</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
@@ -4557,7 +4515,7 @@
         <v>77</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>77</v>
@@ -4568,14 +4526,14 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -4594,16 +4552,16 @@
         <v>77</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="L17" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="M17" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="N17" t="s" s="2">
         <v>190</v>
-      </c>
-      <c r="L17" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="M17" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>193</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -4653,7 +4611,7 @@
         <v>77</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
@@ -4671,7 +4629,7 @@
         <v>77</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>77</v>
@@ -4682,10 +4640,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4711,10 +4669,10 @@
         <v>108</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -4756,7 +4714,7 @@
         <v>112</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>113</v>
+        <v>196</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>77</v>
@@ -4765,7 +4723,7 @@
         <v>141</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -4794,13 +4752,13 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="D19" t="s" s="2">
         <v>77</v>
@@ -4822,13 +4780,13 @@
         <v>77</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="L19" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="M19" t="s" s="2">
         <v>202</v>
-      </c>
-      <c r="L19" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="M19" t="s" s="2">
-        <v>204</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -4879,7 +4837,7 @@
         <v>77</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -4888,7 +4846,7 @@
         <v>79</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>77</v>
+        <v>203</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>116</v>
@@ -4908,13 +4866,13 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="B20" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="C20" t="s" s="2">
         <v>205</v>
-      </c>
-      <c r="B20" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="C20" t="s" s="2">
-        <v>206</v>
       </c>
       <c r="D20" t="s" s="2">
         <v>77</v>
@@ -4936,13 +4894,13 @@
         <v>77</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="L20" t="s" s="2">
         <v>207</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="M20" t="s" s="2">
         <v>208</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>209</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4993,7 +4951,7 @@
         <v>77</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -5002,7 +4960,7 @@
         <v>79</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>77</v>
+        <v>203</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>116</v>
@@ -5022,13 +4980,13 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="B21" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="C21" t="s" s="2">
         <v>210</v>
-      </c>
-      <c r="B21" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="C21" t="s" s="2">
-        <v>211</v>
       </c>
       <c r="D21" t="s" s="2">
         <v>77</v>
@@ -5050,13 +5008,13 @@
         <v>77</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="L21" t="s" s="2">
         <v>212</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="M21" t="s" s="2">
         <v>213</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>214</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -5107,7 +5065,7 @@
         <v>77</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -5116,7 +5074,7 @@
         <v>79</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>77</v>
+        <v>203</v>
       </c>
       <c r="AJ21" t="s" s="2">
         <v>116</v>
@@ -5136,13 +5094,13 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="B22" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="C22" t="s" s="2">
         <v>215</v>
-      </c>
-      <c r="B22" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="C22" t="s" s="2">
-        <v>216</v>
       </c>
       <c r="D22" t="s" s="2">
         <v>77</v>
@@ -5164,13 +5122,13 @@
         <v>77</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="L22" t="s" s="2">
         <v>217</v>
       </c>
-      <c r="L22" t="s" s="2">
+      <c r="M22" t="s" s="2">
         <v>218</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>219</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -5221,7 +5179,7 @@
         <v>77</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -5230,7 +5188,7 @@
         <v>79</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>77</v>
+        <v>203</v>
       </c>
       <c r="AJ22" t="s" s="2">
         <v>116</v>
@@ -5250,13 +5208,13 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="B23" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="C23" t="s" s="2">
         <v>220</v>
-      </c>
-      <c r="B23" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="C23" t="s" s="2">
-        <v>221</v>
       </c>
       <c r="D23" t="s" s="2">
         <v>77</v>
@@ -5278,13 +5236,13 @@
         <v>77</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="L23" t="s" s="2">
         <v>222</v>
       </c>
-      <c r="L23" t="s" s="2">
+      <c r="M23" t="s" s="2">
         <v>223</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>224</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -5335,7 +5293,7 @@
         <v>77</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -5344,7 +5302,7 @@
         <v>79</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>77</v>
+        <v>203</v>
       </c>
       <c r="AJ23" t="s" s="2">
         <v>116</v>
@@ -5364,13 +5322,13 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="B24" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="C24" t="s" s="2">
         <v>225</v>
-      </c>
-      <c r="B24" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="C24" t="s" s="2">
-        <v>226</v>
       </c>
       <c r="D24" t="s" s="2">
         <v>77</v>
@@ -5392,13 +5350,13 @@
         <v>77</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="L24" t="s" s="2">
         <v>227</v>
       </c>
-      <c r="L24" t="s" s="2">
+      <c r="M24" t="s" s="2">
         <v>228</v>
-      </c>
-      <c r="M24" t="s" s="2">
-        <v>229</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -5449,7 +5407,7 @@
         <v>77</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -5458,7 +5416,7 @@
         <v>79</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>77</v>
+        <v>203</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>116</v>
@@ -5478,10 +5436,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5507,16 +5465,16 @@
         <v>108</v>
       </c>
       <c r="L25" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="M25" t="s" s="2">
         <v>231</v>
-      </c>
-      <c r="M25" t="s" s="2">
-        <v>232</v>
       </c>
       <c r="N25" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>77</v>
@@ -5553,19 +5511,19 @@
         <v>77</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>112</v>
+        <v>77</v>
       </c>
       <c r="AC25" t="s" s="2">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="AD25" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>114</v>
+        <v>77</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -5583,7 +5541,7 @@
         <v>77</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>77</v>
@@ -5594,10 +5552,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5620,13 +5578,13 @@
         <v>77</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="L26" t="s" s="2">
         <v>236</v>
       </c>
-      <c r="L26" t="s" s="2">
+      <c r="M26" t="s" s="2">
         <v>237</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>238</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -5665,10 +5623,10 @@
         <v>77</v>
       </c>
       <c r="AB26" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="AC26" t="s" s="2">
         <v>239</v>
-      </c>
-      <c r="AC26" t="s" s="2">
-        <v>240</v>
       </c>
       <c r="AD26" t="s" s="2">
         <v>77</v>
@@ -5677,7 +5635,7 @@
         <v>141</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -5686,33 +5644,33 @@
         <v>79</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>155</v>
+        <v>77</v>
       </c>
       <c r="AJ26" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK26" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="AL26" t="s" s="2">
         <v>241</v>
       </c>
-      <c r="AL26" t="s" s="2">
+      <c r="AM26" t="s" s="2">
         <v>242</v>
       </c>
-      <c r="AM26" t="s" s="2">
-        <v>243</v>
-      </c>
       <c r="AN26" t="s" s="2">
-        <v>244</v>
+        <v>77</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C27" t="s" s="2">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="D27" t="s" s="2">
         <v>77</v>
@@ -5734,13 +5692,13 @@
         <v>77</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="L27" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>247</v>
-      </c>
-      <c r="L27" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>249</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -5791,7 +5749,7 @@
         <v>77</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -5800,33 +5758,33 @@
         <v>79</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>155</v>
+        <v>77</v>
       </c>
       <c r="AJ27" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK27" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="AL27" t="s" s="2">
         <v>241</v>
       </c>
-      <c r="AL27" t="s" s="2">
+      <c r="AM27" t="s" s="2">
         <v>242</v>
       </c>
-      <c r="AM27" t="s" s="2">
-        <v>243</v>
-      </c>
       <c r="AN27" t="s" s="2">
-        <v>244</v>
+        <v>77</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C28" t="s" s="2">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D28" t="s" s="2">
         <v>77</v>
@@ -5848,13 +5806,13 @@
         <v>77</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -5905,7 +5863,7 @@
         <v>77</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -5914,30 +5872,30 @@
         <v>79</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>155</v>
+        <v>77</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK28" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="AL28" t="s" s="2">
         <v>241</v>
       </c>
-      <c r="AL28" t="s" s="2">
+      <c r="AM28" t="s" s="2">
         <v>242</v>
       </c>
-      <c r="AM28" t="s" s="2">
-        <v>243</v>
-      </c>
       <c r="AN28" t="s" s="2">
-        <v>244</v>
+        <v>77</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -6046,10 +6004,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6160,10 +6118,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6186,19 +6144,19 @@
         <v>88</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="L31" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="M31" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="N31" t="s" s="2">
         <v>260</v>
       </c>
-      <c r="M31" t="s" s="2">
+      <c r="O31" t="s" s="2">
         <v>261</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>263</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>77</v>
@@ -6223,31 +6181,31 @@
         <v>77</v>
       </c>
       <c r="X31" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="Y31" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="Z31" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="Y31" t="s" s="2">
+      <c r="AA31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF31" t="s" s="2">
         <v>265</v>
-      </c>
-      <c r="Z31" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="AA31" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB31" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC31" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD31" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE31" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF31" t="s" s="2">
-        <v>267</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -6265,21 +6223,21 @@
         <v>77</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>195</v>
+        <v>192</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6302,19 +6260,19 @@
         <v>88</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="L32" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="M32" t="s" s="2">
         <v>271</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="N32" t="s" s="2">
         <v>272</v>
       </c>
-      <c r="M32" t="s" s="2">
+      <c r="O32" t="s" s="2">
         <v>273</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>275</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>77</v>
@@ -6342,29 +6300,29 @@
         <v>151</v>
       </c>
       <c r="Y32" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="Z32" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="AA32" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB32" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC32" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD32" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE32" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF32" t="s" s="2">
         <v>276</v>
       </c>
-      <c r="Z32" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="AA32" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB32" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC32" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD32" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE32" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF32" t="s" s="2">
-        <v>278</v>
-      </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
       </c>
@@ -6372,7 +6330,7 @@
         <v>87</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>155</v>
+        <v>77</v>
       </c>
       <c r="AJ32" t="s" s="2">
         <v>99</v>
@@ -6381,21 +6339,21 @@
         <v>77</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6421,65 +6379,65 @@
         <v>129</v>
       </c>
       <c r="L33" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="M33" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="N33" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="M33" t="s" s="2">
+      <c r="O33" t="s" s="2">
         <v>283</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>285</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q33" s="2"/>
       <c r="R33" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="S33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T33" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="U33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF33" t="s" s="2">
         <v>286</v>
-      </c>
-      <c r="S33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T33" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="U33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF33" t="s" s="2">
-        <v>288</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -6497,21 +6455,21 @@
         <v>77</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6537,13 +6495,13 @@
         <v>101</v>
       </c>
       <c r="L34" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="M34" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="N34" t="s" s="2">
         <v>293</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>295</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -6557,7 +6515,7 @@
         <v>77</v>
       </c>
       <c r="T34" t="s" s="2">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="U34" t="s" s="2">
         <v>77</v>
@@ -6593,7 +6551,7 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -6611,21 +6569,21 @@
         <v>77</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>299</v>
+        <v>297</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6648,17 +6606,15 @@
         <v>88</v>
       </c>
       <c r="K35" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="L35" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="M35" t="s" s="2">
         <v>302</v>
       </c>
-      <c r="L35" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>305</v>
-      </c>
+      <c r="N35" s="2"/>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>77</v>
@@ -6707,7 +6663,7 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -6716,30 +6672,30 @@
         <v>87</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>155</v>
+        <v>77</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>307</v>
+        <v>99</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>309</v>
+        <v>305</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6762,16 +6718,16 @@
         <v>88</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -6821,7 +6777,7 @@
         <v>77</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -6830,33 +6786,33 @@
         <v>87</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>155</v>
+        <v>77</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>317</v>
+        <v>99</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>319</v>
+        <v>314</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C37" t="s" s="2">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="D37" t="s" s="2">
         <v>77</v>
@@ -6878,13 +6834,13 @@
         <v>77</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6935,7 +6891,7 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -6944,30 +6900,30 @@
         <v>79</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>155</v>
+        <v>77</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK37" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="AL37" t="s" s="2">
         <v>241</v>
       </c>
-      <c r="AL37" t="s" s="2">
+      <c r="AM37" t="s" s="2">
         <v>242</v>
       </c>
-      <c r="AM37" t="s" s="2">
-        <v>243</v>
-      </c>
       <c r="AN37" t="s" s="2">
-        <v>244</v>
+        <v>77</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6990,19 +6946,17 @@
         <v>88</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>327</v>
-      </c>
+        <v>321</v>
+      </c>
+      <c r="N38" s="2"/>
       <c r="O38" t="s" s="2">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>77</v>
@@ -7051,7 +7005,7 @@
         <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -7066,10 +7020,10 @@
         <v>99</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>77</v>
@@ -7080,10 +7034,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7109,16 +7063,14 @@
         <v>129</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>333</v>
-      </c>
+        <v>326</v>
+      </c>
+      <c r="N39" s="2"/>
       <c r="O39" t="s" s="2">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>77</v>
@@ -7167,7 +7119,7 @@
         <v>77</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -7182,10 +7134,10 @@
         <v>99</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>77</v>
@@ -7196,10 +7148,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7222,17 +7174,15 @@
         <v>88</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>340</v>
-      </c>
+        <v>332</v>
+      </c>
+      <c r="N40" s="2"/>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>77</v>
@@ -7281,7 +7231,7 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -7290,16 +7240,16 @@
         <v>79</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>155</v>
+        <v>77</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>317</v>
+        <v>99</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>77</v>
@@ -7310,10 +7260,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>343</v>
+        <v>335</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>343</v>
+        <v>335</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7336,17 +7286,17 @@
         <v>88</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" t="s" s="2">
-        <v>346</v>
+        <v>338</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>77</v>
@@ -7395,7 +7345,7 @@
         <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>343</v>
+        <v>335</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -7404,30 +7354,30 @@
         <v>87</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>155</v>
+        <v>77</v>
       </c>
       <c r="AJ41" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>348</v>
+        <v>340</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>244</v>
+        <v>77</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>349</v>
+        <v>341</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>349</v>
+        <v>341</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7450,19 +7400,19 @@
         <v>88</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>350</v>
+        <v>342</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>352</v>
+        <v>344</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>353</v>
+        <v>345</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>77</v>
@@ -7511,7 +7461,7 @@
         <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>349</v>
+        <v>341</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -7520,16 +7470,16 @@
         <v>79</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>155</v>
+        <v>77</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>317</v>
+        <v>99</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>355</v>
+        <v>347</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>356</v>
+        <v>348</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>77</v>
@@ -7540,10 +7490,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>357</v>
+        <v>349</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>357</v>
+        <v>349</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7566,17 +7516,17 @@
         <v>88</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>358</v>
+        <v>350</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>359</v>
+        <v>351</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
-        <v>360</v>
+        <v>352</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>77</v>
@@ -7601,13 +7551,13 @@
         <v>77</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>359</v>
+        <v>351</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>361</v>
+        <v>353</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>77</v>
@@ -7625,7 +7575,7 @@
         <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>357</v>
+        <v>349</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>87</v>
@@ -7640,13 +7590,13 @@
         <v>99</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>362</v>
+        <v>354</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>363</v>
+        <v>355</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>364</v>
+        <v>356</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>77</v>
@@ -7654,10 +7604,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7680,16 +7630,16 @@
         <v>88</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>366</v>
+        <v>358</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>367</v>
+        <v>359</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>368</v>
+        <v>360</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7715,10 +7665,10 @@
         <v>77</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>369</v>
+        <v>361</v>
       </c>
       <c r="Z44" t="s" s="2">
         <v>77</v>
@@ -7739,7 +7689,7 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -7748,7 +7698,7 @@
         <v>87</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>155</v>
+        <v>77</v>
       </c>
       <c r="AJ44" t="s" s="2">
         <v>99</v>
@@ -7757,21 +7707,21 @@
         <v>77</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>370</v>
+        <v>362</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>371</v>
+        <v>77</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>372</v>
+        <v>363</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>372</v>
+        <v>363</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7794,19 +7744,17 @@
         <v>88</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>373</v>
+        <v>364</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>375</v>
-      </c>
+        <v>365</v>
+      </c>
+      <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>77</v>
@@ -7831,10 +7779,10 @@
         <v>77</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>377</v>
+        <v>367</v>
       </c>
       <c r="Z45" t="s" s="2">
         <v>77</v>
@@ -7855,7 +7803,7 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>372</v>
+        <v>363</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -7864,7 +7812,7 @@
         <v>87</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>155</v>
+        <v>77</v>
       </c>
       <c r="AJ45" t="s" s="2">
         <v>99</v>
@@ -7873,21 +7821,21 @@
         <v>77</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>378</v>
+        <v>368</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>371</v>
+        <v>77</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>379</v>
+        <v>369</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>379</v>
+        <v>369</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7910,16 +7858,16 @@
         <v>88</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>381</v>
+        <v>371</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>382</v>
+        <v>372</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7927,7 +7875,7 @@
       </c>
       <c r="Q46" s="2"/>
       <c r="R46" t="s" s="2">
-        <v>383</v>
+        <v>373</v>
       </c>
       <c r="S46" t="s" s="2">
         <v>77</v>
@@ -7945,13 +7893,13 @@
         <v>77</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>384</v>
+        <v>374</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>385</v>
+        <v>375</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>77</v>
@@ -7969,7 +7917,7 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>379</v>
+        <v>369</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>87</v>
@@ -7984,13 +7932,13 @@
         <v>99</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>386</v>
+        <v>376</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>387</v>
+        <v>377</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>388</v>
+        <v>378</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>77</v>
@@ -7998,10 +7946,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>389</v>
+        <v>379</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>389</v>
+        <v>379</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8024,23 +7972,23 @@
         <v>77</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>391</v>
+        <v>381</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" t="s" s="2">
-        <v>392</v>
+        <v>382</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q47" t="s" s="2">
-        <v>393</v>
+        <v>383</v>
       </c>
       <c r="R47" t="s" s="2">
         <v>77</v>
@@ -8061,13 +8009,13 @@
         <v>77</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>395</v>
+        <v>385</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>77</v>
@@ -8085,7 +8033,7 @@
         <v>77</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>389</v>
+        <v>379</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -8100,13 +8048,13 @@
         <v>99</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>396</v>
+        <v>386</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>397</v>
+        <v>387</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>398</v>
+        <v>388</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>77</v>
@@ -8114,10 +8062,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>399</v>
+        <v>389</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>399</v>
+        <v>389</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8140,16 +8088,16 @@
         <v>88</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>400</v>
+        <v>390</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>401</v>
+        <v>391</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>402</v>
+        <v>392</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -8175,13 +8123,13 @@
         <v>77</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>403</v>
+        <v>393</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>404</v>
+        <v>394</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>77</v>
@@ -8199,7 +8147,7 @@
         <v>77</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>399</v>
+        <v>389</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -8208,30 +8156,30 @@
         <v>87</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>155</v>
+        <v>77</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>405</v>
+        <v>395</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>406</v>
+        <v>396</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>407</v>
+        <v>397</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>371</v>
+        <v>77</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>408</v>
+        <v>398</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>408</v>
+        <v>398</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8257,14 +8205,12 @@
         <v>101</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>409</v>
+        <v>399</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>411</v>
-      </c>
+        <v>400</v>
+      </c>
+      <c r="N49" s="2"/>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>77</v>
@@ -8313,7 +8259,7 @@
         <v>77</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>408</v>
+        <v>398</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -8331,7 +8277,7 @@
         <v>77</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>412</v>
+        <v>401</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>77</v>
@@ -8342,10 +8288,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>413</v>
+        <v>402</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>413</v>
+        <v>402</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8368,19 +8314,19 @@
         <v>88</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>414</v>
+        <v>403</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>415</v>
+        <v>404</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>416</v>
+        <v>405</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>417</v>
+        <v>406</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>77</v>
@@ -8429,7 +8375,7 @@
         <v>77</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>413</v>
+        <v>402</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -8438,19 +8384,19 @@
         <v>87</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>155</v>
+        <v>77</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>317</v>
+        <v>99</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>418</v>
+        <v>407</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>407</v>
+        <v>397</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>77</v>
@@ -8458,14 +8404,14 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>419</v>
+        <v>408</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>419</v>
+        <v>408</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>420</v>
+        <v>409</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -8484,19 +8430,17 @@
         <v>88</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>421</v>
+        <v>410</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>340</v>
-      </c>
+        <v>411</v>
+      </c>
+      <c r="N51" s="2"/>
       <c r="O51" t="s" s="2">
-        <v>423</v>
+        <v>412</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>77</v>
@@ -8545,7 +8489,7 @@
         <v>77</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>419</v>
+        <v>408</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -8554,19 +8498,19 @@
         <v>87</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>155</v>
+        <v>77</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>317</v>
+        <v>99</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>424</v>
+        <v>413</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>425</v>
+        <v>414</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>426</v>
+        <v>415</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>77</v>
@@ -8574,10 +8518,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>427</v>
+        <v>416</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>427</v>
+        <v>416</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8686,10 +8630,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>428</v>
+        <v>417</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>428</v>
+        <v>417</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8800,10 +8744,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>429</v>
+        <v>418</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>429</v>
+        <v>418</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8829,13 +8773,13 @@
         <v>101</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>430</v>
+        <v>419</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>431</v>
+        <v>420</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>432</v>
+        <v>421</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8885,7 +8829,7 @@
         <v>77</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>433</v>
+        <v>422</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -8894,7 +8838,7 @@
         <v>87</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>434</v>
+        <v>423</v>
       </c>
       <c r="AJ54" t="s" s="2">
         <v>99</v>
@@ -8903,7 +8847,7 @@
         <v>77</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>77</v>
@@ -8914,10 +8858,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>435</v>
+        <v>424</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>435</v>
+        <v>424</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8943,13 +8887,13 @@
         <v>129</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>436</v>
+        <v>425</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>437</v>
+        <v>426</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>438</v>
+        <v>427</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8978,10 +8922,10 @@
         <v>151</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>439</v>
+        <v>428</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>77</v>
@@ -8999,7 +8943,7 @@
         <v>77</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>441</v>
+        <v>430</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -9017,7 +8961,7 @@
         <v>77</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>77</v>
@@ -9028,10 +8972,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>442</v>
+        <v>431</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>442</v>
+        <v>431</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9054,16 +8998,16 @@
         <v>88</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>443</v>
+        <v>432</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>444</v>
+        <v>433</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>445</v>
+        <v>434</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>446</v>
+        <v>435</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -9113,7 +9057,7 @@
         <v>77</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>447</v>
+        <v>436</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -9122,7 +9066,7 @@
         <v>87</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>155</v>
+        <v>77</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>99</v>
@@ -9131,21 +9075,21 @@
         <v>77</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>244</v>
+        <v>77</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>449</v>
+        <v>438</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>449</v>
+        <v>438</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9171,13 +9115,13 @@
         <v>101</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>450</v>
+        <v>439</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>451</v>
+        <v>440</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>452</v>
+        <v>441</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -9227,7 +9171,7 @@
         <v>77</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>453</v>
+        <v>442</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -9245,7 +9189,7 @@
         <v>77</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>77</v>
@@ -9256,10 +9200,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>454</v>
+        <v>443</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>454</v>
+        <v>443</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9282,19 +9226,17 @@
         <v>88</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>455</v>
+        <v>444</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>456</v>
+        <v>445</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>340</v>
-      </c>
+        <v>446</v>
+      </c>
+      <c r="N58" s="2"/>
       <c r="O58" t="s" s="2">
-        <v>458</v>
+        <v>447</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>77</v>
@@ -9343,7 +9285,7 @@
         <v>77</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>454</v>
+        <v>443</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -9352,19 +9294,19 @@
         <v>87</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>155</v>
+        <v>77</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>317</v>
+        <v>99</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>459</v>
+        <v>448</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>460</v>
+        <v>449</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>461</v>
+        <v>450</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>77</v>
@@ -9372,10 +9314,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>462</v>
+        <v>451</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>462</v>
+        <v>451</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9398,17 +9340,15 @@
         <v>88</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>463</v>
+        <v>452</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>464</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>305</v>
-      </c>
+        <v>453</v>
+      </c>
+      <c r="N59" s="2"/>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>77</v>
@@ -9457,7 +9397,7 @@
         <v>77</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>462</v>
+        <v>451</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -9466,34 +9406,34 @@
         <v>87</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>155</v>
+        <v>77</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>307</v>
+        <v>99</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>465</v>
+        <v>454</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>466</v>
+        <v>455</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>467</v>
+        <v>456</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>468</v>
+        <v>77</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>469</v>
+        <v>457</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>469</v>
+        <v>457</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>470</v>
+        <v>458</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -9512,17 +9452,17 @@
         <v>77</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>471</v>
+        <v>459</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>472</v>
+        <v>460</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>473</v>
+        <v>461</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
-        <v>474</v>
+        <v>462</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>77</v>
@@ -9571,7 +9511,7 @@
         <v>77</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>469</v>
+        <v>457</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -9580,19 +9520,19 @@
         <v>87</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>475</v>
+        <v>463</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>476</v>
+        <v>464</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>477</v>
+        <v>465</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>478</v>
+        <v>466</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>77</v>
@@ -9600,14 +9540,14 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>480</v>
+        <v>468</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
@@ -9626,17 +9566,17 @@
         <v>88</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>471</v>
+        <v>459</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>481</v>
+        <v>469</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>482</v>
+        <v>470</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" t="s" s="2">
-        <v>483</v>
+        <v>471</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>77</v>
@@ -9685,7 +9625,7 @@
         <v>77</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -9694,7 +9634,7 @@
         <v>87</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>475</v>
+        <v>463</v>
       </c>
       <c r="AJ61" t="s" s="2">
         <v>99</v>
@@ -9703,7 +9643,7 @@
         <v>77</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>484</v>
+        <v>472</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>77</v>
@@ -9714,10 +9654,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>485</v>
+        <v>473</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>485</v>
+        <v>473</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9740,19 +9680,17 @@
         <v>88</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>486</v>
+        <v>474</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>487</v>
+        <v>475</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>340</v>
-      </c>
+        <v>476</v>
+      </c>
+      <c r="N62" s="2"/>
       <c r="O62" t="s" s="2">
-        <v>489</v>
+        <v>477</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>77</v>
@@ -9801,7 +9739,7 @@
         <v>77</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>485</v>
+        <v>473</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -9810,19 +9748,19 @@
         <v>87</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>155</v>
+        <v>77</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>317</v>
+        <v>99</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>490</v>
+        <v>478</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>491</v>
+        <v>479</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>492</v>
+        <v>480</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>77</v>
@@ -9830,10 +9768,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>493</v>
+        <v>481</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>493</v>
+        <v>481</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9856,19 +9794,17 @@
         <v>77</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>494</v>
+        <v>482</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>375</v>
-      </c>
+        <v>483</v>
+      </c>
+      <c r="N63" s="2"/>
       <c r="O63" t="s" s="2">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>77</v>
@@ -9893,13 +9829,13 @@
         <v>77</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>497</v>
+        <v>485</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>498</v>
+        <v>486</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>77</v>
@@ -9917,7 +9853,7 @@
         <v>77</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>493</v>
+        <v>481</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -9926,30 +9862,30 @@
         <v>79</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>155</v>
+        <v>77</v>
       </c>
       <c r="AJ63" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>499</v>
+        <v>487</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>500</v>
+        <v>488</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>501</v>
+        <v>489</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>371</v>
+        <v>77</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>502</v>
+        <v>490</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>502</v>
+        <v>490</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10058,10 +9994,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>503</v>
+        <v>491</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>503</v>
+        <v>491</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10172,10 +10108,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>504</v>
+        <v>492</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>504</v>
+        <v>492</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10201,16 +10137,16 @@
         <v>147</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>505</v>
+        <v>493</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>506</v>
+        <v>494</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>507</v>
+        <v>495</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>508</v>
+        <v>496</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>77</v>
@@ -10235,11 +10171,11 @@
         <v>77</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="Y66" s="2"/>
       <c r="Z66" t="s" s="2">
-        <v>509</v>
+        <v>497</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>77</v>
@@ -10257,7 +10193,7 @@
         <v>77</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>510</v>
+        <v>498</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
@@ -10266,7 +10202,7 @@
         <v>79</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>155</v>
+        <v>77</v>
       </c>
       <c r="AJ66" t="s" s="2">
         <v>99</v>
@@ -10275,21 +10211,21 @@
         <v>77</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>511</v>
+        <v>499</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>512</v>
+        <v>500</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>513</v>
+        <v>501</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>513</v>
+        <v>501</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10315,16 +10251,16 @@
         <v>101</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>514</v>
+        <v>502</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>515</v>
+        <v>503</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>516</v>
+        <v>504</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>517</v>
+        <v>505</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>77</v>
@@ -10373,7 +10309,7 @@
         <v>77</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>518</v>
+        <v>506</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
@@ -10391,25 +10327,25 @@
         <v>77</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>519</v>
+        <v>507</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>520</v>
+        <v>508</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>521</v>
+        <v>509</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>521</v>
+        <v>509</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>522</v>
+        <v>510</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
@@ -10428,19 +10364,19 @@
         <v>88</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>523</v>
+        <v>511</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>524</v>
+        <v>512</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>525</v>
+        <v>513</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>526</v>
+        <v>514</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>527</v>
+        <v>515</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>77</v>
@@ -10489,7 +10425,7 @@
         <v>77</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>521</v>
+        <v>509</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
@@ -10498,19 +10434,19 @@
         <v>87</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>155</v>
+        <v>77</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>317</v>
+        <v>99</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>528</v>
+        <v>516</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>529</v>
+        <v>517</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>501</v>
+        <v>489</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>77</v>
@@ -10518,10 +10454,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>530</v>
+        <v>518</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>530</v>
+        <v>518</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10544,19 +10480,17 @@
         <v>88</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>531</v>
+        <v>519</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>532</v>
+        <v>520</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>533</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>340</v>
-      </c>
+        <v>521</v>
+      </c>
+      <c r="N69" s="2"/>
       <c r="O69" t="s" s="2">
-        <v>534</v>
+        <v>522</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>77</v>
@@ -10605,7 +10539,7 @@
         <v>77</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>530</v>
+        <v>518</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
@@ -10614,19 +10548,19 @@
         <v>87</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>155</v>
+        <v>77</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>317</v>
+        <v>99</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>535</v>
+        <v>523</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>536</v>
+        <v>524</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>537</v>
+        <v>525</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>77</v>
@@ -10634,10 +10568,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>538</v>
+        <v>526</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>538</v>
+        <v>526</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10660,16 +10594,16 @@
         <v>77</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>539</v>
+        <v>527</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>540</v>
+        <v>528</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>541</v>
+        <v>529</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -10695,10 +10629,10 @@
         <v>77</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>542</v>
+        <v>530</v>
       </c>
       <c r="Z70" t="s" s="2">
         <v>77</v>
@@ -10719,7 +10653,7 @@
         <v>77</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>538</v>
+        <v>526</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
@@ -10728,30 +10662,30 @@
         <v>87</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>155</v>
+        <v>77</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>543</v>
+        <v>531</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>544</v>
+        <v>532</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>545</v>
+        <v>533</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>546</v>
+        <v>534</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>547</v>
+        <v>535</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>547</v>
+        <v>535</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10774,16 +10708,16 @@
         <v>77</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>539</v>
+        <v>527</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>548</v>
+        <v>536</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>549</v>
+        <v>537</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10833,7 +10767,7 @@
         <v>77</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>547</v>
+        <v>535</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
@@ -10842,19 +10776,19 @@
         <v>87</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>155</v>
+        <v>77</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>317</v>
+        <v>99</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>550</v>
+        <v>538</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>551</v>
+        <v>539</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>545</v>
+        <v>533</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>77</v>
@@ -10862,10 +10796,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>552</v>
+        <v>540</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>552</v>
+        <v>540</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10888,17 +10822,15 @@
         <v>77</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>553</v>
+        <v>541</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>554</v>
+        <v>542</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>555</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>340</v>
-      </c>
+        <v>543</v>
+      </c>
+      <c r="N72" s="2"/>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>77</v>
@@ -10947,7 +10879,7 @@
         <v>77</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>552</v>
+        <v>540</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>78</v>
@@ -10956,30 +10888,30 @@
         <v>79</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>155</v>
+        <v>77</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>317</v>
+        <v>99</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>556</v>
+        <v>544</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>557</v>
+        <v>545</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>558</v>
+        <v>546</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>559</v>
+        <v>547</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>559</v>
+        <v>547</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11002,17 +10934,15 @@
         <v>77</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>560</v>
+        <v>548</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>561</v>
+        <v>549</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>562</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>563</v>
-      </c>
+        <v>550</v>
+      </c>
+      <c r="N73" s="2"/>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>77</v>
@@ -11061,7 +10991,7 @@
         <v>77</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>559</v>
+        <v>547</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
@@ -11070,34 +11000,34 @@
         <v>79</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>155</v>
+        <v>77</v>
       </c>
       <c r="AJ73" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>564</v>
+        <v>551</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>565</v>
+        <v>552</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>195</v>
+        <v>77</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>566</v>
+        <v>553</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>566</v>
+        <v>553</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>567</v>
+        <v>554</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -11116,16 +11046,16 @@
         <v>77</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>568</v>
+        <v>555</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>569</v>
+        <v>556</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>570</v>
+        <v>557</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>571</v>
+        <v>558</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -11175,7 +11105,7 @@
         <v>77</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>566</v>
+        <v>553</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
@@ -11184,16 +11114,16 @@
         <v>79</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>155</v>
+        <v>77</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>317</v>
+        <v>99</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>572</v>
+        <v>559</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>573</v>
+        <v>560</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>77</v>
@@ -11204,10 +11134,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>574</v>
+        <v>561</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>574</v>
+        <v>561</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11230,17 +11160,17 @@
         <v>77</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>575</v>
+        <v>562</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>577</v>
+        <v>564</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" t="s" s="2">
-        <v>578</v>
+        <v>565</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>77</v>
@@ -11289,7 +11219,7 @@
         <v>77</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>574</v>
+        <v>561</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>
@@ -11298,7 +11228,7 @@
         <v>87</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>155</v>
+        <v>77</v>
       </c>
       <c r="AJ75" t="s" s="2">
         <v>99</v>
@@ -11307,7 +11237,7 @@
         <v>77</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>579</v>
+        <v>566</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>77</v>
@@ -11318,10 +11248,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>580</v>
+        <v>567</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>580</v>
+        <v>567</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11430,10 +11360,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>581</v>
+        <v>568</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>581</v>
+        <v>568</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11503,16 +11433,16 @@
         <v>77</v>
       </c>
       <c r="AB77" t="s" s="2">
-        <v>112</v>
+        <v>77</v>
       </c>
       <c r="AC77" t="s" s="2">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="AD77" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE77" t="s" s="2">
-        <v>114</v>
+        <v>77</v>
       </c>
       <c r="AF77" t="s" s="2">
         <v>115</v>
@@ -11544,14 +11474,14 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>582</v>
+        <v>569</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>582</v>
+        <v>569</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>583</v>
+        <v>570</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
@@ -11573,16 +11503,16 @@
         <v>108</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>584</v>
+        <v>571</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>585</v>
+        <v>572</v>
       </c>
       <c r="N78" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>77</v>
@@ -11631,7 +11561,7 @@
         <v>77</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>586</v>
+        <v>573</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
@@ -11649,7 +11579,7 @@
         <v>77</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="AM78" t="s" s="2">
         <v>77</v>
@@ -11660,10 +11590,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>587</v>
+        <v>574</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>587</v>
+        <v>574</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11686,17 +11616,17 @@
         <v>77</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>588</v>
+        <v>575</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>589</v>
+        <v>576</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>590</v>
+        <v>577</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" t="s" s="2">
-        <v>591</v>
+        <v>578</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>77</v>
@@ -11745,7 +11675,7 @@
         <v>77</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>587</v>
+        <v>574</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>78</v>
@@ -11763,7 +11693,7 @@
         <v>77</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>592</v>
+        <v>579</v>
       </c>
       <c r="AM79" t="s" s="2">
         <v>77</v>
@@ -11774,10 +11704,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>593</v>
+        <v>580</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>593</v>
+        <v>580</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11800,19 +11730,19 @@
         <v>77</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>594</v>
+        <v>581</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>595</v>
+        <v>582</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>596</v>
+        <v>583</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>597</v>
+        <v>584</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>77</v>
@@ -11861,7 +11791,7 @@
         <v>77</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>593</v>
+        <v>580</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>78</v>
@@ -11870,30 +11800,30 @@
         <v>87</v>
       </c>
       <c r="AI80" t="s" s="2">
-        <v>155</v>
+        <v>77</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>307</v>
+        <v>99</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>598</v>
+        <v>585</v>
       </c>
       <c r="AM80" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>468</v>
+        <v>77</v>
       </c>
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>599</v>
+        <v>586</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>599</v>
+        <v>586</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11916,17 +11846,15 @@
         <v>77</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>600</v>
+        <v>587</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>601</v>
+        <v>588</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>602</v>
-      </c>
-      <c r="N81" t="s" s="2">
-        <v>340</v>
-      </c>
+        <v>589</v>
+      </c>
+      <c r="N81" s="2"/>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
         <v>77</v>
@@ -11975,7 +11903,7 @@
         <v>77</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>599</v>
+        <v>586</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>78</v>
@@ -11984,16 +11912,16 @@
         <v>79</v>
       </c>
       <c r="AI81" t="s" s="2">
-        <v>155</v>
+        <v>77</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>317</v>
+        <v>99</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>603</v>
+        <v>590</v>
       </c>
       <c r="AM81" t="s" s="2">
         <v>77</v>
@@ -12004,14 +11932,14 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>604</v>
+        <v>591</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>604</v>
+        <v>591</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>605</v>
+        <v>592</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
@@ -12030,17 +11958,17 @@
         <v>77</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>575</v>
+        <v>562</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>606</v>
+        <v>593</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>607</v>
+        <v>594</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" t="s" s="2">
-        <v>608</v>
+        <v>595</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>77</v>
@@ -12077,7 +12005,7 @@
         <v>77</v>
       </c>
       <c r="AB82" t="s" s="2">
-        <v>609</v>
+        <v>596</v>
       </c>
       <c r="AC82" s="2"/>
       <c r="AD82" t="s" s="2">
@@ -12087,7 +12015,7 @@
         <v>141</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>604</v>
+        <v>591</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>78</v>
@@ -12096,7 +12024,7 @@
         <v>79</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>155</v>
+        <v>77</v>
       </c>
       <c r="AJ82" t="s" s="2">
         <v>99</v>
@@ -12105,7 +12033,7 @@
         <v>77</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>610</v>
+        <v>597</v>
       </c>
       <c r="AM82" t="s" s="2">
         <v>77</v>
@@ -12116,10 +12044,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>611</v>
+        <v>598</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>611</v>
+        <v>598</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12228,10 +12156,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>612</v>
+        <v>599</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>612</v>
+        <v>599</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12301,16 +12229,16 @@
         <v>77</v>
       </c>
       <c r="AB84" t="s" s="2">
-        <v>112</v>
+        <v>77</v>
       </c>
       <c r="AC84" t="s" s="2">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="AD84" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE84" t="s" s="2">
-        <v>114</v>
+        <v>77</v>
       </c>
       <c r="AF84" t="s" s="2">
         <v>115</v>
@@ -12342,14 +12270,14 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>613</v>
+        <v>600</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>613</v>
+        <v>600</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>583</v>
+        <v>570</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
@@ -12371,16 +12299,16 @@
         <v>108</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>584</v>
+        <v>571</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>585</v>
+        <v>572</v>
       </c>
       <c r="N85" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O85" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>77</v>
@@ -12429,7 +12357,7 @@
         <v>77</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>586</v>
+        <v>573</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>78</v>
@@ -12447,7 +12375,7 @@
         <v>77</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="AM85" t="s" s="2">
         <v>77</v>
@@ -12458,14 +12386,14 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>614</v>
+        <v>601</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>614</v>
+        <v>601</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
-        <v>615</v>
+        <v>602</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
@@ -12484,19 +12412,19 @@
         <v>77</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>616</v>
+        <v>603</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>617</v>
+        <v>604</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>618</v>
+        <v>605</v>
       </c>
       <c r="O86" t="s" s="2">
-        <v>619</v>
+        <v>606</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>77</v>
@@ -12521,10 +12449,10 @@
         <v>77</v>
       </c>
       <c r="X86" t="s" s="2">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="Y86" t="s" s="2">
-        <v>620</v>
+        <v>607</v>
       </c>
       <c r="Z86" t="s" s="2">
         <v>77</v>
@@ -12545,7 +12473,7 @@
         <v>77</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>614</v>
+        <v>601</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>87</v>
@@ -12554,7 +12482,7 @@
         <v>87</v>
       </c>
       <c r="AI86" t="s" s="2">
-        <v>155</v>
+        <v>77</v>
       </c>
       <c r="AJ86" t="s" s="2">
         <v>99</v>
@@ -12563,21 +12491,21 @@
         <v>77</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>610</v>
+        <v>597</v>
       </c>
       <c r="AM86" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>371</v>
+        <v>77</v>
       </c>
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>621</v>
+        <v>608</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>621</v>
+        <v>608</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12600,13 +12528,13 @@
         <v>77</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>622</v>
+        <v>609</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>623</v>
+        <v>610</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>624</v>
+        <v>611</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -12657,7 +12585,7 @@
         <v>77</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>621</v>
+        <v>608</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>87</v>
@@ -12666,7 +12594,7 @@
         <v>87</v>
       </c>
       <c r="AI87" t="s" s="2">
-        <v>155</v>
+        <v>77</v>
       </c>
       <c r="AJ87" t="s" s="2">
         <v>99</v>
@@ -12675,7 +12603,7 @@
         <v>77</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>610</v>
+        <v>597</v>
       </c>
       <c r="AM87" t="s" s="2">
         <v>77</v>
@@ -12686,16 +12614,16 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>625</v>
+        <v>612</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>604</v>
+        <v>591</v>
       </c>
       <c r="C88" t="s" s="2">
-        <v>626</v>
+        <v>613</v>
       </c>
       <c r="D88" t="s" s="2">
-        <v>605</v>
+        <v>592</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
@@ -12714,17 +12642,17 @@
         <v>77</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>575</v>
+        <v>562</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>627</v>
+        <v>614</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>628</v>
+        <v>615</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" t="s" s="2">
-        <v>608</v>
+        <v>595</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>77</v>
@@ -12773,7 +12701,7 @@
         <v>77</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>604</v>
+        <v>591</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>78</v>
@@ -12782,7 +12710,7 @@
         <v>79</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>155</v>
+        <v>77</v>
       </c>
       <c r="AJ88" t="s" s="2">
         <v>99</v>
@@ -12791,7 +12719,7 @@
         <v>77</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>610</v>
+        <v>597</v>
       </c>
       <c r="AM88" t="s" s="2">
         <v>77</v>
@@ -12802,10 +12730,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>629</v>
+        <v>616</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>611</v>
+        <v>598</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12914,10 +12842,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>630</v>
+        <v>617</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>612</v>
+        <v>599</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12987,16 +12915,16 @@
         <v>77</v>
       </c>
       <c r="AB90" t="s" s="2">
-        <v>112</v>
+        <v>77</v>
       </c>
       <c r="AC90" t="s" s="2">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="AD90" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE90" t="s" s="2">
-        <v>114</v>
+        <v>77</v>
       </c>
       <c r="AF90" t="s" s="2">
         <v>115</v>
@@ -13028,14 +12956,14 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>631</v>
+        <v>618</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>613</v>
+        <v>600</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>583</v>
+        <v>570</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
@@ -13057,16 +12985,16 @@
         <v>108</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>584</v>
+        <v>571</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>585</v>
+        <v>572</v>
       </c>
       <c r="N91" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>77</v>
@@ -13115,7 +13043,7 @@
         <v>77</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>586</v>
+        <v>573</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>78</v>
@@ -13133,7 +13061,7 @@
         <v>77</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="AM91" t="s" s="2">
         <v>77</v>
@@ -13144,14 +13072,14 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>632</v>
+        <v>619</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>614</v>
+        <v>601</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
-        <v>615</v>
+        <v>602</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
@@ -13170,19 +13098,19 @@
         <v>77</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>616</v>
+        <v>603</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>617</v>
+        <v>604</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>618</v>
+        <v>605</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>619</v>
+        <v>606</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>77</v>
@@ -13207,10 +13135,10 @@
         <v>77</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>620</v>
+        <v>607</v>
       </c>
       <c r="Z92" t="s" s="2">
         <v>77</v>
@@ -13231,7 +13159,7 @@
         <v>77</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>614</v>
+        <v>601</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>87</v>
@@ -13240,7 +13168,7 @@
         <v>87</v>
       </c>
       <c r="AI92" t="s" s="2">
-        <v>155</v>
+        <v>77</v>
       </c>
       <c r="AJ92" t="s" s="2">
         <v>99</v>
@@ -13249,21 +13177,21 @@
         <v>77</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>610</v>
+        <v>597</v>
       </c>
       <c r="AM92" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>371</v>
+        <v>77</v>
       </c>
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>633</v>
+        <v>620</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>634</v>
+        <v>621</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13372,10 +13300,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>635</v>
+        <v>622</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>636</v>
+        <v>623</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13486,10 +13414,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>637</v>
+        <v>624</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>638</v>
+        <v>625</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13515,16 +13443,16 @@
         <v>147</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>505</v>
+        <v>493</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>506</v>
+        <v>494</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>507</v>
+        <v>495</v>
       </c>
       <c r="O95" t="s" s="2">
-        <v>508</v>
+        <v>496</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>77</v>
@@ -13549,11 +13477,11 @@
         <v>77</v>
       </c>
       <c r="X95" t="s" s="2">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="Y95" s="2"/>
       <c r="Z95" t="s" s="2">
-        <v>639</v>
+        <v>626</v>
       </c>
       <c r="AA95" t="s" s="2">
         <v>77</v>
@@ -13571,7 +13499,7 @@
         <v>77</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>510</v>
+        <v>498</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>78</v>
@@ -13580,7 +13508,7 @@
         <v>79</v>
       </c>
       <c r="AI95" t="s" s="2">
-        <v>155</v>
+        <v>77</v>
       </c>
       <c r="AJ95" t="s" s="2">
         <v>99</v>
@@ -13589,21 +13517,21 @@
         <v>77</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>511</v>
+        <v>499</v>
       </c>
       <c r="AM95" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>512</v>
+        <v>500</v>
       </c>
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>640</v>
+        <v>627</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>641</v>
+        <v>628</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13712,10 +13640,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>642</v>
+        <v>629</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>643</v>
+        <v>630</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13826,10 +13754,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>644</v>
+        <v>631</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>645</v>
+        <v>632</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13855,16 +13783,16 @@
         <v>129</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>646</v>
+        <v>633</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>647</v>
+        <v>634</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>648</v>
+        <v>635</v>
       </c>
       <c r="O98" t="s" s="2">
-        <v>649</v>
+        <v>636</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>77</v>
@@ -13913,7 +13841,7 @@
         <v>77</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>650</v>
+        <v>637</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>78</v>
@@ -13931,21 +13859,21 @@
         <v>77</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>651</v>
+        <v>638</v>
       </c>
       <c r="AM98" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>652</v>
+        <v>639</v>
       </c>
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>653</v>
+        <v>640</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>654</v>
+        <v>641</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13971,13 +13899,13 @@
         <v>101</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>655</v>
+        <v>642</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>656</v>
+        <v>643</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>657</v>
+        <v>644</v>
       </c>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
@@ -14027,7 +13955,7 @@
         <v>77</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>658</v>
+        <v>645</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>78</v>
@@ -14045,21 +13973,21 @@
         <v>77</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>659</v>
+        <v>646</v>
       </c>
       <c r="AM99" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>660</v>
+        <v>647</v>
       </c>
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>661</v>
+        <v>648</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>662</v>
+        <v>649</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14082,17 +14010,17 @@
         <v>88</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>663</v>
+        <v>650</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>664</v>
+        <v>651</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" t="s" s="2">
-        <v>665</v>
+        <v>652</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>77</v>
@@ -14141,7 +14069,7 @@
         <v>77</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>666</v>
+        <v>653</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>78</v>
@@ -14159,21 +14087,21 @@
         <v>77</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>667</v>
+        <v>654</v>
       </c>
       <c r="AM100" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>668</v>
+        <v>655</v>
       </c>
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>669</v>
+        <v>656</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>670</v>
+        <v>657</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14199,16 +14127,14 @@
         <v>101</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>671</v>
+        <v>658</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>672</v>
-      </c>
-      <c r="N101" t="s" s="2">
-        <v>411</v>
-      </c>
+        <v>659</v>
+      </c>
+      <c r="N101" s="2"/>
       <c r="O101" t="s" s="2">
-        <v>673</v>
+        <v>660</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>77</v>
@@ -14257,7 +14183,7 @@
         <v>77</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>674</v>
+        <v>661</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>78</v>
@@ -14275,21 +14201,21 @@
         <v>77</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>675</v>
+        <v>662</v>
       </c>
       <c r="AM101" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>676</v>
+        <v>663</v>
       </c>
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>677</v>
+        <v>664</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>678</v>
+        <v>665</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14312,19 +14238,19 @@
         <v>88</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>679</v>
+        <v>666</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>680</v>
+        <v>667</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>681</v>
+        <v>668</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>682</v>
+        <v>669</v>
       </c>
       <c r="O102" t="s" s="2">
-        <v>683</v>
+        <v>670</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>77</v>
@@ -14373,7 +14299,7 @@
         <v>77</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>684</v>
+        <v>671</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>78</v>
@@ -14391,21 +14317,21 @@
         <v>77</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>685</v>
+        <v>672</v>
       </c>
       <c r="AM102" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>686</v>
+        <v>673</v>
       </c>
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>687</v>
+        <v>674</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>688</v>
+        <v>675</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14431,16 +14357,16 @@
         <v>101</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>514</v>
+        <v>502</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>515</v>
+        <v>503</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>516</v>
+        <v>504</v>
       </c>
       <c r="O103" t="s" s="2">
-        <v>517</v>
+        <v>505</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>77</v>
@@ -14489,7 +14415,7 @@
         <v>77</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>518</v>
+        <v>506</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>78</v>
@@ -14507,21 +14433,21 @@
         <v>77</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>519</v>
+        <v>507</v>
       </c>
       <c r="AM103" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>520</v>
+        <v>508</v>
       </c>
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>689</v>
+        <v>676</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>621</v>
+        <v>608</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14544,13 +14470,13 @@
         <v>77</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>690</v>
+        <v>677</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>623</v>
+        <v>610</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>624</v>
+        <v>611</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -14601,7 +14527,7 @@
         <v>77</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>621</v>
+        <v>608</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>87</v>
@@ -14610,7 +14536,7 @@
         <v>87</v>
       </c>
       <c r="AI104" t="s" s="2">
-        <v>155</v>
+        <v>77</v>
       </c>
       <c r="AJ104" t="s" s="2">
         <v>99</v>
@@ -14619,7 +14545,7 @@
         <v>77</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>610</v>
+        <v>597</v>
       </c>
       <c r="AM104" t="s" s="2">
         <v>77</v>
@@ -14630,16 +14556,16 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>691</v>
+        <v>678</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>604</v>
+        <v>591</v>
       </c>
       <c r="C105" t="s" s="2">
-        <v>692</v>
+        <v>679</v>
       </c>
       <c r="D105" t="s" s="2">
-        <v>605</v>
+        <v>592</v>
       </c>
       <c r="E105" s="2"/>
       <c r="F105" t="s" s="2">
@@ -14658,17 +14584,17 @@
         <v>77</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>575</v>
+        <v>562</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>693</v>
+        <v>680</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>628</v>
+        <v>615</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" t="s" s="2">
-        <v>608</v>
+        <v>595</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>77</v>
@@ -14717,7 +14643,7 @@
         <v>77</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>604</v>
+        <v>591</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>78</v>
@@ -14726,7 +14652,7 @@
         <v>79</v>
       </c>
       <c r="AI105" t="s" s="2">
-        <v>155</v>
+        <v>77</v>
       </c>
       <c r="AJ105" t="s" s="2">
         <v>99</v>
@@ -14735,7 +14661,7 @@
         <v>77</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>610</v>
+        <v>597</v>
       </c>
       <c r="AM105" t="s" s="2">
         <v>77</v>
@@ -14746,10 +14672,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>694</v>
+        <v>681</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>611</v>
+        <v>598</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14858,10 +14784,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>695</v>
+        <v>682</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>612</v>
+        <v>599</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14931,16 +14857,16 @@
         <v>77</v>
       </c>
       <c r="AB107" t="s" s="2">
-        <v>112</v>
+        <v>77</v>
       </c>
       <c r="AC107" t="s" s="2">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="AD107" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE107" t="s" s="2">
-        <v>114</v>
+        <v>77</v>
       </c>
       <c r="AF107" t="s" s="2">
         <v>115</v>
@@ -14972,14 +14898,14 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>696</v>
+        <v>683</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>613</v>
+        <v>600</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
-        <v>583</v>
+        <v>570</v>
       </c>
       <c r="E108" s="2"/>
       <c r="F108" t="s" s="2">
@@ -15001,16 +14927,16 @@
         <v>108</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>584</v>
+        <v>571</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>585</v>
+        <v>572</v>
       </c>
       <c r="N108" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O108" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>77</v>
@@ -15059,7 +14985,7 @@
         <v>77</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>586</v>
+        <v>573</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>78</v>
@@ -15077,7 +15003,7 @@
         <v>77</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="AM108" t="s" s="2">
         <v>77</v>
@@ -15088,14 +15014,14 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>697</v>
+        <v>684</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>614</v>
+        <v>601</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
-        <v>615</v>
+        <v>602</v>
       </c>
       <c r="E109" s="2"/>
       <c r="F109" t="s" s="2">
@@ -15114,19 +15040,19 @@
         <v>77</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>616</v>
+        <v>603</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>617</v>
+        <v>604</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>618</v>
+        <v>605</v>
       </c>
       <c r="O109" t="s" s="2">
-        <v>619</v>
+        <v>606</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>77</v>
@@ -15151,10 +15077,10 @@
         <v>77</v>
       </c>
       <c r="X109" t="s" s="2">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="Y109" t="s" s="2">
-        <v>620</v>
+        <v>607</v>
       </c>
       <c r="Z109" t="s" s="2">
         <v>77</v>
@@ -15175,7 +15101,7 @@
         <v>77</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>614</v>
+        <v>601</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>87</v>
@@ -15184,7 +15110,7 @@
         <v>87</v>
       </c>
       <c r="AI109" t="s" s="2">
-        <v>155</v>
+        <v>77</v>
       </c>
       <c r="AJ109" t="s" s="2">
         <v>99</v>
@@ -15193,21 +15119,21 @@
         <v>77</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>610</v>
+        <v>597</v>
       </c>
       <c r="AM109" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN109" t="s" s="2">
-        <v>371</v>
+        <v>77</v>
       </c>
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>698</v>
+        <v>685</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>634</v>
+        <v>621</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15316,10 +15242,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>699</v>
+        <v>686</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>636</v>
+        <v>623</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15430,10 +15356,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>700</v>
+        <v>687</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>638</v>
+        <v>625</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15459,16 +15385,16 @@
         <v>147</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>505</v>
+        <v>493</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>506</v>
+        <v>494</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>507</v>
+        <v>495</v>
       </c>
       <c r="O112" t="s" s="2">
-        <v>508</v>
+        <v>496</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>77</v>
@@ -15493,11 +15419,11 @@
         <v>77</v>
       </c>
       <c r="X112" t="s" s="2">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="Y112" s="2"/>
       <c r="Z112" t="s" s="2">
-        <v>639</v>
+        <v>626</v>
       </c>
       <c r="AA112" t="s" s="2">
         <v>77</v>
@@ -15515,7 +15441,7 @@
         <v>77</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>510</v>
+        <v>498</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>78</v>
@@ -15524,7 +15450,7 @@
         <v>79</v>
       </c>
       <c r="AI112" t="s" s="2">
-        <v>155</v>
+        <v>77</v>
       </c>
       <c r="AJ112" t="s" s="2">
         <v>99</v>
@@ -15533,21 +15459,21 @@
         <v>77</v>
       </c>
       <c r="AL112" t="s" s="2">
-        <v>511</v>
+        <v>499</v>
       </c>
       <c r="AM112" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN112" t="s" s="2">
-        <v>512</v>
+        <v>500</v>
       </c>
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>701</v>
+        <v>688</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>641</v>
+        <v>628</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15656,10 +15582,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>702</v>
+        <v>689</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>643</v>
+        <v>630</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15770,10 +15696,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>703</v>
+        <v>690</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>645</v>
+        <v>632</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -15799,16 +15725,16 @@
         <v>129</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>646</v>
+        <v>633</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>647</v>
+        <v>634</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>648</v>
+        <v>635</v>
       </c>
       <c r="O115" t="s" s="2">
-        <v>649</v>
+        <v>636</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>77</v>
@@ -15857,7 +15783,7 @@
         <v>77</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>650</v>
+        <v>637</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>78</v>
@@ -15875,21 +15801,21 @@
         <v>77</v>
       </c>
       <c r="AL115" t="s" s="2">
-        <v>651</v>
+        <v>638</v>
       </c>
       <c r="AM115" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN115" t="s" s="2">
-        <v>652</v>
+        <v>639</v>
       </c>
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>704</v>
+        <v>691</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>654</v>
+        <v>641</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -15915,13 +15841,13 @@
         <v>101</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>655</v>
+        <v>642</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>656</v>
+        <v>643</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>657</v>
+        <v>644</v>
       </c>
       <c r="O116" s="2"/>
       <c r="P116" t="s" s="2">
@@ -15971,7 +15897,7 @@
         <v>77</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>658</v>
+        <v>645</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>78</v>
@@ -15989,21 +15915,21 @@
         <v>77</v>
       </c>
       <c r="AL116" t="s" s="2">
-        <v>659</v>
+        <v>646</v>
       </c>
       <c r="AM116" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN116" t="s" s="2">
-        <v>660</v>
+        <v>647</v>
       </c>
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>705</v>
+        <v>692</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>662</v>
+        <v>649</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16026,24 +15952,24 @@
         <v>88</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>663</v>
+        <v>650</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>664</v>
+        <v>651</v>
       </c>
       <c r="N117" s="2"/>
       <c r="O117" t="s" s="2">
-        <v>665</v>
+        <v>652</v>
       </c>
       <c r="P117" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q117" s="2"/>
       <c r="R117" t="s" s="2">
-        <v>706</v>
+        <v>693</v>
       </c>
       <c r="S117" t="s" s="2">
         <v>77</v>
@@ -16085,7 +16011,7 @@
         <v>77</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>666</v>
+        <v>653</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>78</v>
@@ -16103,21 +16029,21 @@
         <v>77</v>
       </c>
       <c r="AL117" t="s" s="2">
-        <v>667</v>
+        <v>654</v>
       </c>
       <c r="AM117" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN117" t="s" s="2">
-        <v>668</v>
+        <v>655</v>
       </c>
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>707</v>
+        <v>694</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>670</v>
+        <v>657</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16143,16 +16069,14 @@
         <v>101</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>671</v>
+        <v>658</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>672</v>
-      </c>
-      <c r="N118" t="s" s="2">
-        <v>411</v>
-      </c>
+        <v>659</v>
+      </c>
+      <c r="N118" s="2"/>
       <c r="O118" t="s" s="2">
-        <v>673</v>
+        <v>660</v>
       </c>
       <c r="P118" t="s" s="2">
         <v>77</v>
@@ -16201,7 +16125,7 @@
         <v>77</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>674</v>
+        <v>661</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>78</v>
@@ -16219,21 +16143,21 @@
         <v>77</v>
       </c>
       <c r="AL118" t="s" s="2">
-        <v>675</v>
+        <v>662</v>
       </c>
       <c r="AM118" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN118" t="s" s="2">
-        <v>676</v>
+        <v>663</v>
       </c>
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>708</v>
+        <v>695</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>678</v>
+        <v>665</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16256,19 +16180,19 @@
         <v>88</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>679</v>
+        <v>666</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>680</v>
+        <v>667</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>681</v>
+        <v>668</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>682</v>
+        <v>669</v>
       </c>
       <c r="O119" t="s" s="2">
-        <v>683</v>
+        <v>670</v>
       </c>
       <c r="P119" t="s" s="2">
         <v>77</v>
@@ -16317,7 +16241,7 @@
         <v>77</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>684</v>
+        <v>671</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>78</v>
@@ -16335,21 +16259,21 @@
         <v>77</v>
       </c>
       <c r="AL119" t="s" s="2">
-        <v>685</v>
+        <v>672</v>
       </c>
       <c r="AM119" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN119" t="s" s="2">
-        <v>686</v>
+        <v>673</v>
       </c>
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>709</v>
+        <v>696</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>688</v>
+        <v>675</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16375,16 +16299,16 @@
         <v>101</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>514</v>
+        <v>502</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>515</v>
+        <v>503</v>
       </c>
       <c r="N120" t="s" s="2">
-        <v>516</v>
+        <v>504</v>
       </c>
       <c r="O120" t="s" s="2">
-        <v>517</v>
+        <v>505</v>
       </c>
       <c r="P120" t="s" s="2">
         <v>77</v>
@@ -16433,7 +16357,7 @@
         <v>77</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>518</v>
+        <v>506</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>78</v>
@@ -16451,21 +16375,21 @@
         <v>77</v>
       </c>
       <c r="AL120" t="s" s="2">
-        <v>519</v>
+        <v>507</v>
       </c>
       <c r="AM120" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN120" t="s" s="2">
-        <v>520</v>
+        <v>508</v>
       </c>
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>710</v>
+        <v>697</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>621</v>
+        <v>608</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16488,16 +16412,16 @@
         <v>77</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>711</v>
+        <v>698</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>623</v>
+        <v>610</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>624</v>
+        <v>611</v>
       </c>
       <c r="N121" t="s" s="2">
-        <v>712</v>
+        <v>699</v>
       </c>
       <c r="O121" s="2"/>
       <c r="P121" t="s" s="2">
@@ -16547,7 +16471,7 @@
         <v>77</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>621</v>
+        <v>608</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>87</v>
@@ -16556,7 +16480,7 @@
         <v>87</v>
       </c>
       <c r="AI121" t="s" s="2">
-        <v>155</v>
+        <v>77</v>
       </c>
       <c r="AJ121" t="s" s="2">
         <v>99</v>
@@ -16565,7 +16489,7 @@
         <v>77</v>
       </c>
       <c r="AL121" t="s" s="2">
-        <v>610</v>
+        <v>597</v>
       </c>
       <c r="AM121" t="s" s="2">
         <v>77</v>
@@ -16576,10 +16500,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>713</v>
+        <v>700</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>713</v>
+        <v>700</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -16602,17 +16526,17 @@
         <v>77</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>575</v>
+        <v>562</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>714</v>
+        <v>701</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" t="s" s="2">
-        <v>716</v>
+        <v>703</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>77</v>
@@ -16649,7 +16573,7 @@
         <v>77</v>
       </c>
       <c r="AB122" t="s" s="2">
-        <v>609</v>
+        <v>596</v>
       </c>
       <c r="AC122" s="2"/>
       <c r="AD122" t="s" s="2">
@@ -16659,7 +16583,7 @@
         <v>141</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>713</v>
+        <v>700</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>78</v>
@@ -16668,7 +16592,7 @@
         <v>79</v>
       </c>
       <c r="AI122" t="s" s="2">
-        <v>155</v>
+        <v>77</v>
       </c>
       <c r="AJ122" t="s" s="2">
         <v>99</v>
@@ -16677,7 +16601,7 @@
         <v>77</v>
       </c>
       <c r="AL122" t="s" s="2">
-        <v>610</v>
+        <v>597</v>
       </c>
       <c r="AM122" t="s" s="2">
         <v>77</v>
@@ -16688,10 +16612,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>717</v>
+        <v>704</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>717</v>
+        <v>704</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -16800,10 +16724,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>718</v>
+        <v>705</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>718</v>
+        <v>705</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -16873,16 +16797,16 @@
         <v>77</v>
       </c>
       <c r="AB124" t="s" s="2">
-        <v>112</v>
+        <v>77</v>
       </c>
       <c r="AC124" t="s" s="2">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="AD124" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE124" t="s" s="2">
-        <v>114</v>
+        <v>77</v>
       </c>
       <c r="AF124" t="s" s="2">
         <v>115</v>
@@ -16914,14 +16838,14 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>719</v>
+        <v>706</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>719</v>
+        <v>706</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
-        <v>583</v>
+        <v>570</v>
       </c>
       <c r="E125" s="2"/>
       <c r="F125" t="s" s="2">
@@ -16943,16 +16867,16 @@
         <v>108</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>584</v>
+        <v>571</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>585</v>
+        <v>572</v>
       </c>
       <c r="N125" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O125" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>77</v>
@@ -17001,7 +16925,7 @@
         <v>77</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>586</v>
+        <v>573</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>78</v>
@@ -17019,7 +16943,7 @@
         <v>77</v>
       </c>
       <c r="AL125" t="s" s="2">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="AM125" t="s" s="2">
         <v>77</v>
@@ -17030,14 +16954,14 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>720</v>
+        <v>707</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>720</v>
+        <v>707</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
-        <v>615</v>
+        <v>602</v>
       </c>
       <c r="E126" s="2"/>
       <c r="F126" t="s" s="2">
@@ -17056,19 +16980,17 @@
         <v>77</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>721</v>
+        <v>708</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>722</v>
-      </c>
-      <c r="N126" t="s" s="2">
-        <v>375</v>
-      </c>
+        <v>709</v>
+      </c>
+      <c r="N126" s="2"/>
       <c r="O126" t="s" s="2">
-        <v>723</v>
+        <v>710</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>77</v>
@@ -17093,10 +17015,10 @@
         <v>77</v>
       </c>
       <c r="X126" t="s" s="2">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="Y126" t="s" s="2">
-        <v>724</v>
+        <v>711</v>
       </c>
       <c r="Z126" t="s" s="2">
         <v>77</v>
@@ -17117,7 +17039,7 @@
         <v>77</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>720</v>
+        <v>707</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>87</v>
@@ -17126,7 +17048,7 @@
         <v>87</v>
       </c>
       <c r="AI126" t="s" s="2">
-        <v>155</v>
+        <v>77</v>
       </c>
       <c r="AJ126" t="s" s="2">
         <v>99</v>
@@ -17135,21 +17057,21 @@
         <v>77</v>
       </c>
       <c r="AL126" t="s" s="2">
-        <v>610</v>
+        <v>597</v>
       </c>
       <c r="AM126" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN126" t="s" s="2">
-        <v>371</v>
+        <v>77</v>
       </c>
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>725</v>
+        <v>712</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>725</v>
+        <v>712</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17172,17 +17094,17 @@
         <v>77</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>622</v>
+        <v>609</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>726</v>
+        <v>713</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>727</v>
+        <v>714</v>
       </c>
       <c r="N127" s="2"/>
       <c r="O127" t="s" s="2">
-        <v>728</v>
+        <v>715</v>
       </c>
       <c r="P127" t="s" s="2">
         <v>77</v>
@@ -17231,7 +17153,7 @@
         <v>77</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>725</v>
+        <v>712</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>87</v>
@@ -17240,7 +17162,7 @@
         <v>87</v>
       </c>
       <c r="AI127" t="s" s="2">
-        <v>155</v>
+        <v>77</v>
       </c>
       <c r="AJ127" t="s" s="2">
         <v>99</v>
@@ -17249,7 +17171,7 @@
         <v>77</v>
       </c>
       <c r="AL127" t="s" s="2">
-        <v>610</v>
+        <v>597</v>
       </c>
       <c r="AM127" t="s" s="2">
         <v>77</v>
@@ -17260,13 +17182,13 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>729</v>
+        <v>716</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>713</v>
+        <v>700</v>
       </c>
       <c r="C128" t="s" s="2">
-        <v>730</v>
+        <v>717</v>
       </c>
       <c r="D128" t="s" s="2">
         <v>77</v>
@@ -17288,17 +17210,17 @@
         <v>77</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>575</v>
+        <v>562</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>731</v>
+        <v>718</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>732</v>
+        <v>719</v>
       </c>
       <c r="N128" s="2"/>
       <c r="O128" t="s" s="2">
-        <v>716</v>
+        <v>703</v>
       </c>
       <c r="P128" t="s" s="2">
         <v>77</v>
@@ -17347,7 +17269,7 @@
         <v>77</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>713</v>
+        <v>700</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>78</v>
@@ -17356,7 +17278,7 @@
         <v>79</v>
       </c>
       <c r="AI128" t="s" s="2">
-        <v>155</v>
+        <v>77</v>
       </c>
       <c r="AJ128" t="s" s="2">
         <v>99</v>
@@ -17365,7 +17287,7 @@
         <v>77</v>
       </c>
       <c r="AL128" t="s" s="2">
-        <v>610</v>
+        <v>597</v>
       </c>
       <c r="AM128" t="s" s="2">
         <v>77</v>
@@ -17376,10 +17298,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>733</v>
+        <v>720</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>717</v>
+        <v>704</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17488,10 +17410,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>734</v>
+        <v>721</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>718</v>
+        <v>705</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -17561,16 +17483,16 @@
         <v>77</v>
       </c>
       <c r="AB130" t="s" s="2">
-        <v>112</v>
+        <v>77</v>
       </c>
       <c r="AC130" t="s" s="2">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="AD130" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE130" t="s" s="2">
-        <v>114</v>
+        <v>77</v>
       </c>
       <c r="AF130" t="s" s="2">
         <v>115</v>
@@ -17602,14 +17524,14 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>735</v>
+        <v>722</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>719</v>
+        <v>706</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
-        <v>583</v>
+        <v>570</v>
       </c>
       <c r="E131" s="2"/>
       <c r="F131" t="s" s="2">
@@ -17631,16 +17553,16 @@
         <v>108</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>584</v>
+        <v>571</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>585</v>
+        <v>572</v>
       </c>
       <c r="N131" t="s" s="2">
         <v>111</v>
       </c>
       <c r="O131" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="P131" t="s" s="2">
         <v>77</v>
@@ -17689,7 +17611,7 @@
         <v>77</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>586</v>
+        <v>573</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>78</v>
@@ -17707,7 +17629,7 @@
         <v>77</v>
       </c>
       <c r="AL131" t="s" s="2">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="AM131" t="s" s="2">
         <v>77</v>
@@ -17718,14 +17640,14 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>736</v>
+        <v>723</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>720</v>
+        <v>707</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
-        <v>615</v>
+        <v>602</v>
       </c>
       <c r="E132" s="2"/>
       <c r="F132" t="s" s="2">
@@ -17744,19 +17666,17 @@
         <v>77</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>721</v>
+        <v>708</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>722</v>
-      </c>
-      <c r="N132" t="s" s="2">
-        <v>375</v>
-      </c>
+        <v>709</v>
+      </c>
+      <c r="N132" s="2"/>
       <c r="O132" t="s" s="2">
-        <v>723</v>
+        <v>710</v>
       </c>
       <c r="P132" t="s" s="2">
         <v>77</v>
@@ -17781,10 +17701,10 @@
         <v>77</v>
       </c>
       <c r="X132" t="s" s="2">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="Y132" t="s" s="2">
-        <v>724</v>
+        <v>711</v>
       </c>
       <c r="Z132" t="s" s="2">
         <v>77</v>
@@ -17805,7 +17725,7 @@
         <v>77</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>720</v>
+        <v>707</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>87</v>
@@ -17814,7 +17734,7 @@
         <v>87</v>
       </c>
       <c r="AI132" t="s" s="2">
-        <v>155</v>
+        <v>77</v>
       </c>
       <c r="AJ132" t="s" s="2">
         <v>99</v>
@@ -17823,21 +17743,21 @@
         <v>77</v>
       </c>
       <c r="AL132" t="s" s="2">
-        <v>610</v>
+        <v>597</v>
       </c>
       <c r="AM132" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN132" t="s" s="2">
-        <v>371</v>
+        <v>77</v>
       </c>
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>737</v>
+        <v>724</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>738</v>
+        <v>725</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -17946,10 +17866,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>739</v>
+        <v>726</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>740</v>
+        <v>727</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -18060,10 +17980,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>741</v>
+        <v>728</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>742</v>
+        <v>729</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -18089,16 +18009,16 @@
         <v>147</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>505</v>
+        <v>493</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>506</v>
+        <v>494</v>
       </c>
       <c r="N135" t="s" s="2">
-        <v>507</v>
+        <v>495</v>
       </c>
       <c r="O135" t="s" s="2">
-        <v>508</v>
+        <v>496</v>
       </c>
       <c r="P135" t="s" s="2">
         <v>77</v>
@@ -18123,11 +18043,11 @@
         <v>77</v>
       </c>
       <c r="X135" t="s" s="2">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="Y135" s="2"/>
       <c r="Z135" t="s" s="2">
-        <v>639</v>
+        <v>626</v>
       </c>
       <c r="AA135" t="s" s="2">
         <v>77</v>
@@ -18145,7 +18065,7 @@
         <v>77</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>510</v>
+        <v>498</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>78</v>
@@ -18154,7 +18074,7 @@
         <v>79</v>
       </c>
       <c r="AI135" t="s" s="2">
-        <v>155</v>
+        <v>77</v>
       </c>
       <c r="AJ135" t="s" s="2">
         <v>99</v>
@@ -18163,21 +18083,21 @@
         <v>77</v>
       </c>
       <c r="AL135" t="s" s="2">
-        <v>511</v>
+        <v>499</v>
       </c>
       <c r="AM135" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN135" t="s" s="2">
-        <v>512</v>
+        <v>500</v>
       </c>
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>743</v>
+        <v>730</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>744</v>
+        <v>731</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -18286,10 +18206,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>745</v>
+        <v>732</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>746</v>
+        <v>733</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -18400,10 +18320,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>747</v>
+        <v>734</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>748</v>
+        <v>735</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -18429,16 +18349,16 @@
         <v>129</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>646</v>
+        <v>633</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>647</v>
+        <v>634</v>
       </c>
       <c r="N138" t="s" s="2">
-        <v>648</v>
+        <v>635</v>
       </c>
       <c r="O138" t="s" s="2">
-        <v>649</v>
+        <v>636</v>
       </c>
       <c r="P138" t="s" s="2">
         <v>77</v>
@@ -18487,7 +18407,7 @@
         <v>77</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>650</v>
+        <v>637</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>78</v>
@@ -18505,21 +18425,21 @@
         <v>77</v>
       </c>
       <c r="AL138" t="s" s="2">
-        <v>651</v>
+        <v>638</v>
       </c>
       <c r="AM138" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN138" t="s" s="2">
-        <v>652</v>
+        <v>639</v>
       </c>
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>749</v>
+        <v>736</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>750</v>
+        <v>737</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -18545,13 +18465,13 @@
         <v>101</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>655</v>
+        <v>642</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>656</v>
+        <v>643</v>
       </c>
       <c r="N139" t="s" s="2">
-        <v>657</v>
+        <v>644</v>
       </c>
       <c r="O139" s="2"/>
       <c r="P139" t="s" s="2">
@@ -18601,7 +18521,7 @@
         <v>77</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>658</v>
+        <v>645</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>78</v>
@@ -18619,21 +18539,21 @@
         <v>77</v>
       </c>
       <c r="AL139" t="s" s="2">
-        <v>659</v>
+        <v>646</v>
       </c>
       <c r="AM139" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN139" t="s" s="2">
-        <v>660</v>
+        <v>647</v>
       </c>
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>751</v>
+        <v>738</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>752</v>
+        <v>739</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -18656,24 +18576,24 @@
         <v>88</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>663</v>
+        <v>650</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>664</v>
+        <v>651</v>
       </c>
       <c r="N140" s="2"/>
       <c r="O140" t="s" s="2">
-        <v>665</v>
+        <v>652</v>
       </c>
       <c r="P140" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q140" s="2"/>
       <c r="R140" t="s" s="2">
-        <v>753</v>
+        <v>740</v>
       </c>
       <c r="S140" t="s" s="2">
         <v>77</v>
@@ -18715,7 +18635,7 @@
         <v>77</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>666</v>
+        <v>653</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>78</v>
@@ -18733,21 +18653,21 @@
         <v>77</v>
       </c>
       <c r="AL140" t="s" s="2">
-        <v>667</v>
+        <v>654</v>
       </c>
       <c r="AM140" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN140" t="s" s="2">
-        <v>668</v>
+        <v>655</v>
       </c>
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>754</v>
+        <v>741</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>755</v>
+        <v>742</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -18773,16 +18693,14 @@
         <v>101</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>671</v>
+        <v>658</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>672</v>
-      </c>
-      <c r="N141" t="s" s="2">
-        <v>411</v>
-      </c>
+        <v>659</v>
+      </c>
+      <c r="N141" s="2"/>
       <c r="O141" t="s" s="2">
-        <v>673</v>
+        <v>660</v>
       </c>
       <c r="P141" t="s" s="2">
         <v>77</v>
@@ -18831,7 +18749,7 @@
         <v>77</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>674</v>
+        <v>661</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>78</v>
@@ -18849,21 +18767,21 @@
         <v>77</v>
       </c>
       <c r="AL141" t="s" s="2">
-        <v>675</v>
+        <v>662</v>
       </c>
       <c r="AM141" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN141" t="s" s="2">
-        <v>676</v>
+        <v>663</v>
       </c>
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>756</v>
+        <v>743</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>757</v>
+        <v>744</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -18886,19 +18804,19 @@
         <v>88</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>679</v>
+        <v>666</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>680</v>
+        <v>667</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>681</v>
+        <v>668</v>
       </c>
       <c r="N142" t="s" s="2">
-        <v>682</v>
+        <v>669</v>
       </c>
       <c r="O142" t="s" s="2">
-        <v>683</v>
+        <v>670</v>
       </c>
       <c r="P142" t="s" s="2">
         <v>77</v>
@@ -18947,7 +18865,7 @@
         <v>77</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>684</v>
+        <v>671</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>78</v>
@@ -18965,21 +18883,21 @@
         <v>77</v>
       </c>
       <c r="AL142" t="s" s="2">
-        <v>685</v>
+        <v>672</v>
       </c>
       <c r="AM142" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN142" t="s" s="2">
-        <v>686</v>
+        <v>673</v>
       </c>
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>758</v>
+        <v>745</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>759</v>
+        <v>746</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -19005,16 +18923,16 @@
         <v>101</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>514</v>
+        <v>502</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>515</v>
+        <v>503</v>
       </c>
       <c r="N143" t="s" s="2">
-        <v>516</v>
+        <v>504</v>
       </c>
       <c r="O143" t="s" s="2">
-        <v>517</v>
+        <v>505</v>
       </c>
       <c r="P143" t="s" s="2">
         <v>77</v>
@@ -19063,7 +18981,7 @@
         <v>77</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>518</v>
+        <v>506</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>78</v>
@@ -19081,21 +18999,21 @@
         <v>77</v>
       </c>
       <c r="AL143" t="s" s="2">
-        <v>519</v>
+        <v>507</v>
       </c>
       <c r="AM143" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN143" t="s" s="2">
-        <v>520</v>
+        <v>508</v>
       </c>
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>760</v>
+        <v>747</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>725</v>
+        <v>712</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -19118,17 +19036,17 @@
         <v>77</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>761</v>
+        <v>748</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>726</v>
+        <v>713</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>727</v>
+        <v>714</v>
       </c>
       <c r="N144" s="2"/>
       <c r="O144" t="s" s="2">
-        <v>728</v>
+        <v>715</v>
       </c>
       <c r="P144" t="s" s="2">
         <v>77</v>
@@ -19177,7 +19095,7 @@
         <v>77</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>725</v>
+        <v>712</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>87</v>
@@ -19186,7 +19104,7 @@
         <v>87</v>
       </c>
       <c r="AI144" t="s" s="2">
-        <v>155</v>
+        <v>77</v>
       </c>
       <c r="AJ144" t="s" s="2">
         <v>99</v>
@@ -19195,7 +19113,7 @@
         <v>77</v>
       </c>
       <c r="AL144" t="s" s="2">
-        <v>610</v>
+        <v>597</v>
       </c>
       <c r="AM144" t="s" s="2">
         <v>77</v>
